--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_utility_water.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_utility_water.xlsx
@@ -1139,43 +1139,43 @@
         <v>268.007299270073</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>176.982251021625</v>
       </c>
       <c r="G2">
         <v>0.06532038641113121</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.11004196083431</v>
       </c>
       <c r="I2">
         <v>0.00593595260534154</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>410</v>
       </c>
       <c r="L2">
-        <v>412.751163704955</v>
+        <v>408.477857015477</v>
       </c>
       <c r="M2">
         <v>307.548273403076</v>
       </c>
       <c r="N2">
-        <v>307.851163704955</v>
+        <v>307.702339749508</v>
       </c>
       <c r="O2">
         <v>2.44827340307561</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.12448273403076</v>
       </c>
       <c r="Q2">
         <v>0.06766559483080151</v>
       </c>
       <c r="R2">
-        <v>0.0675739638059059</v>
+        <v>0.0676189638059059</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1197,13 +1197,13 @@
         <v>0.0677039848216754</v>
       </c>
       <c r="X2">
-        <v>0.0675739638059059</v>
+        <v>0.0677939028342483</v>
       </c>
       <c r="Y2">
         <v>0.426949434039963</v>
       </c>
       <c r="Z2">
-        <v>0.424415082434625</v>
+        <v>0.428702103469318</v>
       </c>
       <c r="AA2">
         <v>0.2429999999999999</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06757396380590586</v>
+        <v>0.06761896380590586</v>
       </c>
       <c r="C2">
-        <v>412.7511637049546</v>
+        <v>408.4778570154768</v>
       </c>
       <c r="D2">
-        <v>307.8511637049546</v>
+        <v>307.7023397495076</v>
       </c>
       <c r="E2">
-        <v>-2.448273403075607</v>
+        <v>1.67620933095515</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.124482734030757</v>
       </c>
       <c r="G2">
         <v>104.9</v>
@@ -1457,28 +1457,28 @@
         <v>36.717</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.207461481521747</v>
       </c>
       <c r="N2">
-        <v>36.717</v>
+        <v>36.50953851847825</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>36.717</v>
+        <v>36.50953851847825</v>
       </c>
       <c r="Q2">
-        <v>37.481</v>
+        <v>37.27353851847825</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06757396380590586</v>
+        <v>0.06779390283424834</v>
       </c>
       <c r="T2">
-        <v>0.4244150824346248</v>
+        <v>0.428702103469318</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>176.9822510216248</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06761896380590586</v>
+        <v>0.06766396380590584</v>
       </c>
       <c r="C3">
-        <v>408.4778570154768</v>
+        <v>404.2046941478862</v>
       </c>
       <c r="D3">
-        <v>307.7023397495076</v>
+        <v>307.5536596159477</v>
       </c>
       <c r="E3">
-        <v>1.67620933095515</v>
+        <v>5.800692064985906</v>
       </c>
       <c r="F3">
-        <v>4.124482734030757</v>
+        <v>8.248965468061513</v>
       </c>
       <c r="G3">
         <v>104.9</v>
@@ -1539,28 +1539,28 @@
         <v>36.717</v>
       </c>
       <c r="M3">
-        <v>0.207461481521747</v>
+        <v>0.4149229630434941</v>
       </c>
       <c r="N3">
-        <v>36.50953851847825</v>
+        <v>36.3020770369565</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>36.50953851847825</v>
+        <v>36.3020770369565</v>
       </c>
       <c r="Q3">
-        <v>37.27353851847825</v>
+        <v>37.06607703695651</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06779390283424834</v>
+        <v>0.06801833041418964</v>
       </c>
       <c r="T3">
-        <v>0.428702103469318</v>
+        <v>0.4330766147292089</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>176.9822510216248</v>
+        <v>88.49112551081237</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06766396380590584</v>
+        <v>0.06770896380590585</v>
       </c>
       <c r="C4">
-        <v>404.2046941478862</v>
+        <v>399.9316748938012</v>
       </c>
       <c r="D4">
-        <v>307.5536596159477</v>
+        <v>307.4051230958935</v>
       </c>
       <c r="E4">
-        <v>5.800692064985906</v>
+        <v>9.925174799016661</v>
       </c>
       <c r="F4">
-        <v>8.248965468061513</v>
+        <v>12.37344820209227</v>
       </c>
       <c r="G4">
         <v>104.9</v>
@@ -1621,28 +1621,28 @@
         <v>36.717</v>
       </c>
       <c r="M4">
-        <v>0.4149229630434941</v>
+        <v>0.622384444565241</v>
       </c>
       <c r="N4">
-        <v>36.3020770369565</v>
+        <v>36.09461555543476</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>36.3020770369565</v>
+        <v>36.09461555543476</v>
       </c>
       <c r="Q4">
-        <v>37.06607703695651</v>
+        <v>36.85861555543476</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06801833041418964</v>
+        <v>0.06824738536691326</v>
       </c>
       <c r="T4">
-        <v>0.4330766147292089</v>
+        <v>0.4375413220975513</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>88.49112551081237</v>
+        <v>58.99408367387493</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06770896380590585</v>
+        <v>0.06775396380590586</v>
       </c>
       <c r="C5">
-        <v>399.9316748938012</v>
+        <v>395.6587990452433</v>
       </c>
       <c r="D5">
-        <v>307.4051230958935</v>
+        <v>307.2567299813663</v>
       </c>
       <c r="E5">
-        <v>9.925174799016661</v>
+        <v>14.04965753304742</v>
       </c>
       <c r="F5">
-        <v>12.37344820209227</v>
+        <v>16.49793093612303</v>
       </c>
       <c r="G5">
         <v>104.9</v>
@@ -1703,28 +1703,28 @@
         <v>36.717</v>
       </c>
       <c r="M5">
-        <v>0.622384444565241</v>
+        <v>0.8298459260869882</v>
       </c>
       <c r="N5">
-        <v>36.09461555543476</v>
+        <v>35.88715407391301</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>36.09461555543476</v>
+        <v>35.88715407391301</v>
       </c>
       <c r="Q5">
-        <v>36.85861555543476</v>
+        <v>36.65115407391301</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06824738536691326</v>
+        <v>0.0684812122978186</v>
       </c>
       <c r="T5">
-        <v>0.4375413220975513</v>
+        <v>0.4420990442027342</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.99408367387493</v>
+        <v>44.24556275540618</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06775396380590586</v>
+        <v>0.06779896380590586</v>
       </c>
       <c r="C6">
-        <v>395.6587990452433</v>
+        <v>391.3860663946347</v>
       </c>
       <c r="D6">
-        <v>307.2567299813663</v>
+        <v>307.1084800647885</v>
       </c>
       <c r="E6">
-        <v>14.04965753304742</v>
+        <v>18.17414026707818</v>
       </c>
       <c r="F6">
-        <v>16.49793093612303</v>
+        <v>20.62241367015378</v>
       </c>
       <c r="G6">
         <v>104.9</v>
@@ -1785,28 +1785,28 @@
         <v>36.717</v>
       </c>
       <c r="M6">
-        <v>0.8298459260869882</v>
+        <v>1.037307407608735</v>
       </c>
       <c r="N6">
-        <v>35.88715407391301</v>
+        <v>35.67969259239126</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>35.88715407391301</v>
+        <v>35.67969259239126</v>
       </c>
       <c r="Q6">
-        <v>36.65115407391301</v>
+        <v>36.44369259239127</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0684812122978186</v>
+        <v>0.06871996190095353</v>
       </c>
       <c r="T6">
-        <v>0.4420990442027342</v>
+        <v>0.4467527183522366</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.24556275540618</v>
+        <v>35.39645020432495</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06779896380590586</v>
+        <v>0.06784396380590586</v>
       </c>
       <c r="C7">
-        <v>391.3860663946347</v>
+        <v>387.1134767347986</v>
       </c>
       <c r="D7">
-        <v>307.1084800647885</v>
+        <v>306.9603731389832</v>
       </c>
       <c r="E7">
-        <v>18.17414026707818</v>
+        <v>22.29862300110893</v>
       </c>
       <c r="F7">
-        <v>20.62241367015378</v>
+        <v>24.74689640418454</v>
       </c>
       <c r="G7">
         <v>104.9</v>
@@ -1867,28 +1867,28 @@
         <v>36.717</v>
       </c>
       <c r="M7">
-        <v>1.037307407608735</v>
+        <v>1.244768889130482</v>
       </c>
       <c r="N7">
-        <v>35.67969259239126</v>
+        <v>35.47223111086952</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>35.67969259239126</v>
+        <v>35.47223111086952</v>
       </c>
       <c r="Q7">
-        <v>36.44369259239127</v>
+        <v>36.23623111086952</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06871996190095353</v>
+        <v>0.06896379128287858</v>
       </c>
       <c r="T7">
-        <v>0.4467527183522366</v>
+        <v>0.4515054068453455</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.39645020432495</v>
+        <v>29.49704183693746</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06784396380590585</v>
+        <v>0.06788896380590585</v>
       </c>
       <c r="C8">
-        <v>387.1134767347987</v>
+        <v>382.8410298589575</v>
       </c>
       <c r="D8">
-        <v>306.9603731389833</v>
+        <v>306.8124089971728</v>
       </c>
       <c r="E8">
-        <v>22.29862300110893</v>
+        <v>26.42310573513969</v>
       </c>
       <c r="F8">
-        <v>24.74689640418454</v>
+        <v>28.87137913821529</v>
       </c>
       <c r="G8">
         <v>104.9</v>
@@ -1949,28 +1949,28 @@
         <v>36.717</v>
       </c>
       <c r="M8">
-        <v>1.244768889130482</v>
+        <v>1.452230370652229</v>
       </c>
       <c r="N8">
-        <v>35.47223111086952</v>
+        <v>35.26476962934777</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>35.47223111086952</v>
+        <v>35.26476962934777</v>
       </c>
       <c r="Q8">
-        <v>36.23623111086952</v>
+        <v>36.02876962934777</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06896379128287858</v>
+        <v>0.06921286430742565</v>
       </c>
       <c r="T8">
-        <v>0.4515054068453455</v>
+        <v>0.4563603036931449</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.49704183693746</v>
+        <v>25.28317871737497</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06788896380590585</v>
+        <v>0.06793396380590587</v>
       </c>
       <c r="C9">
-        <v>382.8410298589575</v>
+        <v>378.5687255607322</v>
       </c>
       <c r="D9">
-        <v>306.8124089971728</v>
+        <v>306.6645874329782</v>
       </c>
       <c r="E9">
-        <v>26.42310573513969</v>
+        <v>30.54758846917045</v>
       </c>
       <c r="F9">
-        <v>28.8713791382153</v>
+        <v>32.99586187224605</v>
       </c>
       <c r="G9">
         <v>104.9</v>
@@ -2031,28 +2031,28 @@
         <v>36.717</v>
       </c>
       <c r="M9">
-        <v>1.452230370652229</v>
+        <v>1.659691852173976</v>
       </c>
       <c r="N9">
-        <v>35.26476962934777</v>
+        <v>35.05730814782602</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>35.26476962934777</v>
+        <v>35.05730814782602</v>
       </c>
       <c r="Q9">
-        <v>36.02876962934777</v>
+        <v>35.82130814782602</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06921286430742565</v>
+        <v>0.06946735196294115</v>
       </c>
       <c r="T9">
-        <v>0.4563603036931449</v>
+        <v>0.461320741776766</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.28317871737496</v>
+        <v>22.12278137770309</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06793396380590587</v>
+        <v>0.06797896380590587</v>
       </c>
       <c r="C10">
-        <v>378.5687255607322</v>
+        <v>374.2965636341411</v>
       </c>
       <c r="D10">
-        <v>306.6645874329782</v>
+        <v>306.5169082404179</v>
       </c>
       <c r="E10">
-        <v>30.54758846917045</v>
+        <v>34.6720712032012</v>
       </c>
       <c r="F10">
-        <v>32.99586187224605</v>
+        <v>37.1203446062768</v>
       </c>
       <c r="G10">
         <v>104.9</v>
@@ -2113,28 +2113,28 @@
         <v>36.717</v>
       </c>
       <c r="M10">
-        <v>1.659691852173976</v>
+        <v>1.867153333695723</v>
       </c>
       <c r="N10">
-        <v>35.05730814782602</v>
+        <v>34.84984666630427</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>35.05730814782602</v>
+        <v>34.84984666630427</v>
       </c>
       <c r="Q10">
-        <v>35.82130814782602</v>
+        <v>35.61384666630428</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06946735196294115</v>
+        <v>0.06972743275374271</v>
       </c>
       <c r="T10">
-        <v>0.461320741776766</v>
+        <v>0.4663902004776097</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.12278137770309</v>
+        <v>19.66469455795831</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06797896380590587</v>
+        <v>0.06802396380590586</v>
       </c>
       <c r="C11">
-        <v>374.2965636341411</v>
+        <v>370.0245438735993</v>
       </c>
       <c r="D11">
-        <v>306.5169082404179</v>
+        <v>306.3693712139069</v>
       </c>
       <c r="E11">
-        <v>34.6720712032012</v>
+        <v>38.79655393723196</v>
       </c>
       <c r="F11">
-        <v>37.1203446062768</v>
+        <v>41.24482734030756</v>
       </c>
       <c r="G11">
         <v>104.9</v>
@@ -2195,28 +2195,28 @@
         <v>36.717</v>
       </c>
       <c r="M11">
-        <v>1.867153333695723</v>
+        <v>2.07461481521747</v>
       </c>
       <c r="N11">
-        <v>34.84984666630427</v>
+        <v>34.64238518478253</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>34.84984666630427</v>
+        <v>34.64238518478253</v>
       </c>
       <c r="Q11">
-        <v>35.61384666630428</v>
+        <v>35.40638518478253</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06972743275374271</v>
+        <v>0.06999329311767317</v>
       </c>
       <c r="T11">
-        <v>0.4663902004776097</v>
+        <v>0.4715723138162498</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.66469455795831</v>
+        <v>17.69822510216248</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06802396380590586</v>
+        <v>0.06806896380590585</v>
       </c>
       <c r="C12">
-        <v>370.0245438735993</v>
+        <v>365.7526660739176</v>
       </c>
       <c r="D12">
-        <v>306.3693712139069</v>
+        <v>306.2219761482559</v>
       </c>
       <c r="E12">
-        <v>38.79655393723196</v>
+        <v>42.92103667126272</v>
       </c>
       <c r="F12">
-        <v>41.24482734030757</v>
+        <v>45.36931007433832</v>
       </c>
       <c r="G12">
         <v>104.9</v>
@@ -2277,28 +2277,28 @@
         <v>36.717</v>
       </c>
       <c r="M12">
-        <v>2.07461481521747</v>
+        <v>2.282076296739218</v>
       </c>
       <c r="N12">
-        <v>34.64238518478253</v>
+        <v>34.43492370326078</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>34.64238518478253</v>
+        <v>34.43492370326078</v>
       </c>
       <c r="Q12">
-        <v>35.40638518478253</v>
+        <v>35.19892370326078</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06999329311767317</v>
+        <v>0.07026512787180433</v>
       </c>
       <c r="T12">
-        <v>0.4715723138162498</v>
+        <v>0.4768708791400279</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.69822510216247</v>
+        <v>16.08929554742043</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06806896380590585</v>
+        <v>0.06811396380590584</v>
       </c>
       <c r="C13">
-        <v>365.7526660739176</v>
+        <v>361.4809300303013</v>
       </c>
       <c r="D13">
-        <v>306.2219761482559</v>
+        <v>306.0747228386703</v>
       </c>
       <c r="E13">
-        <v>42.92103667126272</v>
+        <v>47.04551940529347</v>
       </c>
       <c r="F13">
-        <v>45.36931007433832</v>
+        <v>49.49379280836907</v>
       </c>
       <c r="G13">
         <v>104.9</v>
@@ -2359,28 +2359,28 @@
         <v>36.717</v>
       </c>
       <c r="M13">
-        <v>2.282076296739218</v>
+        <v>2.489537778260964</v>
       </c>
       <c r="N13">
-        <v>34.43492370326078</v>
+        <v>34.22746222173903</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>34.43492370326078</v>
+        <v>34.22746222173903</v>
       </c>
       <c r="Q13">
-        <v>35.19892370326078</v>
+        <v>34.99146222173903</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07026512787180433</v>
+        <v>0.07054314068852938</v>
       </c>
       <c r="T13">
-        <v>0.4768708791400279</v>
+        <v>0.4822898664029827</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.08929554742043</v>
+        <v>14.74852091846873</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06811396380590584</v>
+        <v>0.06815896380590586</v>
       </c>
       <c r="C14">
-        <v>361.4809300303013</v>
+        <v>357.2093355383493</v>
       </c>
       <c r="D14">
-        <v>306.0747228386703</v>
+        <v>305.9276110807491</v>
       </c>
       <c r="E14">
-        <v>47.04551940529347</v>
+        <v>51.17000213932423</v>
       </c>
       <c r="F14">
-        <v>49.49379280836907</v>
+        <v>53.61827554239984</v>
       </c>
       <c r="G14">
         <v>104.9</v>
@@ -2441,28 +2441,28 @@
         <v>36.717</v>
       </c>
       <c r="M14">
-        <v>2.489537778260964</v>
+        <v>2.696999259782712</v>
       </c>
       <c r="N14">
-        <v>34.22746222173903</v>
+        <v>34.02000074021728</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>34.22746222173903</v>
+        <v>34.02000074021728</v>
       </c>
       <c r="Q14">
-        <v>34.99146222173903</v>
+        <v>34.78400074021729</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07054314068852938</v>
+        <v>0.07082754460448949</v>
       </c>
       <c r="T14">
-        <v>0.4822898664029827</v>
+        <v>0.4878334280857756</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.74852091846873</v>
+        <v>13.61401930935575</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06815896380590586</v>
+        <v>0.06841396380590586</v>
       </c>
       <c r="C15">
-        <v>357.2093355383493</v>
+        <v>352.2538834373226</v>
       </c>
       <c r="D15">
-        <v>305.9276110807491</v>
+        <v>305.0966417137532</v>
       </c>
       <c r="E15">
-        <v>51.17000213932423</v>
+        <v>55.29448487335499</v>
       </c>
       <c r="F15">
-        <v>53.61827554239984</v>
+        <v>57.74275827643059</v>
       </c>
       <c r="G15">
         <v>104.9</v>
@@ -2523,45 +2523,45 @@
         <v>36.717</v>
       </c>
       <c r="M15">
-        <v>2.696999259782712</v>
+        <v>2.991074878719105</v>
       </c>
       <c r="N15">
-        <v>34.02000074021728</v>
+        <v>33.72592512128089</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>34.02000074021728</v>
+        <v>33.72592512128089</v>
       </c>
       <c r="Q15">
-        <v>34.78400074021729</v>
+        <v>34.4899251212809</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07082754460448949</v>
+        <v>0.07111856256500682</v>
       </c>
       <c r="T15">
-        <v>0.4878334280857756</v>
+        <v>0.4935059098077033</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.61401930935575</v>
+        <v>12.2755201687641</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06841396380590586</v>
+        <v>0.06847396380590585</v>
       </c>
       <c r="C16">
-        <v>352.2538834373226</v>
+        <v>347.9345341240154</v>
       </c>
       <c r="D16">
-        <v>305.0966417137532</v>
+        <v>304.9017751344768</v>
       </c>
       <c r="E16">
-        <v>55.29448487335499</v>
+        <v>59.41896760738575</v>
       </c>
       <c r="F16">
-        <v>57.74275827643059</v>
+        <v>61.86724101046136</v>
       </c>
       <c r="G16">
         <v>104.9</v>
@@ -2605,28 +2605,28 @@
         <v>36.717</v>
       </c>
       <c r="M16">
-        <v>2.991074878719105</v>
+        <v>3.204723084341898</v>
       </c>
       <c r="N16">
-        <v>33.72592512128089</v>
+        <v>33.5122769156581</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>33.72592512128089</v>
+        <v>33.5122769156581</v>
       </c>
       <c r="Q16">
-        <v>34.4899251212809</v>
+        <v>34.2762769156581</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07111856256500682</v>
+        <v>0.07141642800694807</v>
       </c>
       <c r="T16">
-        <v>0.4935059098077033</v>
+        <v>0.4993118616877939</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.2755201687641</v>
+        <v>11.45715215751316</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06847396380590585</v>
+        <v>0.06853396380590585</v>
       </c>
       <c r="C17">
-        <v>347.9345341240154</v>
+        <v>343.615433576119</v>
       </c>
       <c r="D17">
-        <v>304.9017751344768</v>
+        <v>304.7071573206111</v>
       </c>
       <c r="E17">
-        <v>59.41896760738574</v>
+        <v>63.5434503414165</v>
       </c>
       <c r="F17">
-        <v>61.86724101046134</v>
+        <v>65.99172374449211</v>
       </c>
       <c r="G17">
         <v>104.9</v>
@@ -2687,28 +2687,28 @@
         <v>36.717</v>
       </c>
       <c r="M17">
-        <v>3.204723084341897</v>
+        <v>3.418371289964691</v>
       </c>
       <c r="N17">
-        <v>33.5122769156581</v>
+        <v>33.29862871003531</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>33.5122769156581</v>
+        <v>33.29862871003531</v>
       </c>
       <c r="Q17">
-        <v>34.2762769156581</v>
+        <v>34.06262871003531</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07141642800694807</v>
+        <v>0.07172138548322125</v>
       </c>
       <c r="T17">
-        <v>0.4993118616877939</v>
+        <v>0.5052560505174104</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.45715215751316</v>
+        <v>10.74108014766859</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06853396380590585</v>
+        <v>0.06859396380590586</v>
       </c>
       <c r="C18">
-        <v>343.615433576119</v>
+        <v>339.2965813175785</v>
       </c>
       <c r="D18">
-        <v>304.7071573206111</v>
+        <v>304.5127877961014</v>
       </c>
       <c r="E18">
-        <v>63.5434503414165</v>
+        <v>67.66793307544727</v>
       </c>
       <c r="F18">
-        <v>65.99172374449211</v>
+        <v>70.11620647852287</v>
       </c>
       <c r="G18">
         <v>104.9</v>
@@ -2769,28 +2769,28 @@
         <v>36.717</v>
       </c>
       <c r="M18">
-        <v>3.418371289964691</v>
+        <v>3.632019495587484</v>
       </c>
       <c r="N18">
-        <v>33.29862871003531</v>
+        <v>33.08498050441251</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>33.29862871003531</v>
+        <v>33.08498050441251</v>
       </c>
       <c r="Q18">
-        <v>34.06262871003531</v>
+        <v>33.84898050441252</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07172138548322125</v>
+        <v>0.0720336913324167</v>
       </c>
       <c r="T18">
-        <v>0.5052560505174104</v>
+        <v>0.511343472812801</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.74108014766859</v>
+        <v>10.10925190368808</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06859396380590586</v>
+        <v>0.06895996380590586</v>
       </c>
       <c r="C19">
-        <v>339.2965813175785</v>
+        <v>333.9917935167921</v>
       </c>
       <c r="D19">
-        <v>304.5127877961014</v>
+        <v>303.3324827293457</v>
       </c>
       <c r="E19">
-        <v>67.66793307544727</v>
+        <v>71.79241580947802</v>
       </c>
       <c r="F19">
-        <v>70.11620647852287</v>
+        <v>74.24068921255362</v>
       </c>
       <c r="G19">
         <v>104.9</v>
@@ -2851,45 +2851,45 @@
         <v>36.717</v>
       </c>
       <c r="M19">
-        <v>3.632019495587484</v>
+        <v>3.971876872871619</v>
       </c>
       <c r="N19">
-        <v>33.08498050441251</v>
+        <v>32.74512312712838</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>33.08498050441251</v>
+        <v>32.74512312712838</v>
       </c>
       <c r="Q19">
-        <v>33.84898050441252</v>
+        <v>33.50912312712838</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0720336913324167</v>
+        <v>0.07235361439744617</v>
       </c>
       <c r="T19">
-        <v>0.511343472812801</v>
+        <v>0.5175793688227132</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.10925190368808</v>
+        <v>9.244244264161708</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06895996380590586</v>
+        <v>0.06903696380590586</v>
       </c>
       <c r="C20">
-        <v>333.9917935167921</v>
+        <v>329.6201592581922</v>
       </c>
       <c r="D20">
-        <v>303.3324827293457</v>
+        <v>303.0853312047765</v>
       </c>
       <c r="E20">
-        <v>71.792415809478</v>
+        <v>75.91689854350876</v>
       </c>
       <c r="F20">
-        <v>74.2406892125536</v>
+        <v>78.36517194658437</v>
       </c>
       <c r="G20">
         <v>104.9</v>
@@ -2933,28 +2933,28 @@
         <v>36.717</v>
       </c>
       <c r="M20">
-        <v>3.971876872871618</v>
+        <v>4.192536699142264</v>
       </c>
       <c r="N20">
-        <v>32.74512312712838</v>
+        <v>32.52446330085773</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>32.74512312712838</v>
+        <v>32.52446330085773</v>
       </c>
       <c r="Q20">
-        <v>33.50912312712838</v>
+        <v>33.28846330085774</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07235361439744617</v>
+        <v>0.07268143679741464</v>
       </c>
       <c r="T20">
-        <v>0.5175793688227132</v>
+        <v>0.5239692375736108</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.24424426416171</v>
+        <v>8.757705092363722</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06903696380590586</v>
+        <v>0.06911396380590586</v>
       </c>
       <c r="C21">
-        <v>329.6201592581922</v>
+        <v>325.248927423663</v>
       </c>
       <c r="D21">
-        <v>303.0853312047765</v>
+        <v>302.8385821042781</v>
       </c>
       <c r="E21">
-        <v>75.91689854350876</v>
+        <v>80.04138127753953</v>
       </c>
       <c r="F21">
-        <v>78.36517194658437</v>
+        <v>82.48965468061513</v>
       </c>
       <c r="G21">
         <v>104.9</v>
@@ -3015,28 +3015,28 @@
         <v>36.717</v>
       </c>
       <c r="M21">
-        <v>4.192536699142264</v>
+        <v>4.41319652541291</v>
       </c>
       <c r="N21">
-        <v>32.52446330085773</v>
+        <v>32.30380347458709</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>32.52446330085773</v>
+        <v>32.30380347458709</v>
       </c>
       <c r="Q21">
-        <v>33.28846330085774</v>
+        <v>33.06780347458709</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07268143679741464</v>
+        <v>0.07301745475738232</v>
       </c>
       <c r="T21">
-        <v>0.5239692375736108</v>
+        <v>0.5305188530432809</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.757705092363722</v>
+        <v>8.319819837745538</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06911396380590586</v>
+        <v>0.06919096380590586</v>
       </c>
       <c r="C22">
-        <v>325.248927423663</v>
+        <v>320.8780970311345</v>
       </c>
       <c r="D22">
-        <v>302.8385821042781</v>
+        <v>302.5922344457803</v>
       </c>
       <c r="E22">
-        <v>80.04138127753953</v>
+        <v>84.16586401157029</v>
       </c>
       <c r="F22">
-        <v>82.48965468061513</v>
+        <v>86.6141374146459</v>
       </c>
       <c r="G22">
         <v>104.9</v>
@@ -3097,28 +3097,28 @@
         <v>36.717</v>
       </c>
       <c r="M22">
-        <v>4.41319652541291</v>
+        <v>4.633856351683555</v>
       </c>
       <c r="N22">
-        <v>32.30380347458709</v>
+        <v>32.08314364831644</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>32.30380347458709</v>
+        <v>32.08314364831644</v>
       </c>
       <c r="Q22">
-        <v>33.06780347458709</v>
+        <v>32.84714364831645</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07301745475738232</v>
+        <v>0.07336197950114666</v>
       </c>
       <c r="T22">
-        <v>0.5305188530432809</v>
+        <v>0.5372342815628162</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.319819837745538</v>
+        <v>7.923637940710035</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06919096380590586</v>
+        <v>0.06944396380590587</v>
       </c>
       <c r="C23">
-        <v>320.8780970311345</v>
+        <v>315.9470006350234</v>
       </c>
       <c r="D23">
-        <v>302.5922344457803</v>
+        <v>301.7856207837</v>
       </c>
       <c r="E23">
-        <v>84.16586401157028</v>
+        <v>88.29034674560104</v>
       </c>
       <c r="F23">
-        <v>86.61413741464588</v>
+        <v>90.73862014867665</v>
       </c>
       <c r="G23">
         <v>104.9</v>
@@ -3179,45 +3179,45 @@
         <v>36.717</v>
       </c>
       <c r="M23">
-        <v>4.633856351683555</v>
+        <v>4.927107074073142</v>
       </c>
       <c r="N23">
-        <v>32.08314364831644</v>
+        <v>31.78989292592686</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>32.08314364831644</v>
+        <v>31.78989292592686</v>
       </c>
       <c r="Q23">
-        <v>32.84714364831645</v>
+        <v>32.55389292592686</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07336197950114666</v>
+        <v>0.07371533821269982</v>
       </c>
       <c r="T23">
-        <v>0.5372342815628162</v>
+        <v>0.5441219005572112</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.923637940710035</v>
+        <v>7.452040202902833</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06944396380590587</v>
+        <v>0.06952896380590586</v>
       </c>
       <c r="C24">
-        <v>315.9470006350234</v>
+        <v>311.5524854428626</v>
       </c>
       <c r="D24">
-        <v>301.7856207837</v>
+        <v>301.51558832557</v>
       </c>
       <c r="E24">
-        <v>88.29034674560104</v>
+        <v>92.41482947963179</v>
       </c>
       <c r="F24">
-        <v>90.73862014867665</v>
+        <v>94.86310288270739</v>
       </c>
       <c r="G24">
         <v>104.9</v>
@@ -3261,28 +3261,28 @@
         <v>36.717</v>
       </c>
       <c r="M24">
-        <v>4.927107074073142</v>
+        <v>5.151066486531012</v>
       </c>
       <c r="N24">
-        <v>31.78989292592686</v>
+        <v>31.56593351346899</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>31.78989292592686</v>
+        <v>31.56593351346899</v>
       </c>
       <c r="Q24">
-        <v>32.55389292592686</v>
+        <v>32.32993351346899</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07371533821269982</v>
+        <v>0.07407787507260501</v>
       </c>
       <c r="T24">
-        <v>0.5441219005572112</v>
+        <v>0.5511884187462659</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.452040202902833</v>
+        <v>7.128038454950536</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06952896380590586</v>
+        <v>0.06961396380590587</v>
       </c>
       <c r="C25">
-        <v>311.5524854428626</v>
+        <v>307.1584530592681</v>
       </c>
       <c r="D25">
-        <v>301.51558832557</v>
+        <v>301.2460386760062</v>
       </c>
       <c r="E25">
-        <v>92.41482947963179</v>
+        <v>96.53931221366255</v>
       </c>
       <c r="F25">
-        <v>94.86310288270739</v>
+        <v>98.98758561673816</v>
       </c>
       <c r="G25">
         <v>104.9</v>
@@ -3343,28 +3343,28 @@
         <v>36.717</v>
       </c>
       <c r="M25">
-        <v>5.151066486531012</v>
+        <v>5.375025898988882</v>
       </c>
       <c r="N25">
-        <v>31.56593351346899</v>
+        <v>31.34197410101112</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>31.56593351346899</v>
+        <v>31.34197410101112</v>
       </c>
       <c r="Q25">
-        <v>32.32993351346899</v>
+        <v>32.10597410101112</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07407787507260501</v>
+        <v>0.07444995237619192</v>
       </c>
       <c r="T25">
-        <v>0.5511884187462659</v>
+        <v>0.5584408979402958</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.128038454950536</v>
+        <v>6.83103685266093</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06961396380590586</v>
+        <v>0.06969896380590586</v>
       </c>
       <c r="C26">
-        <v>307.1584530592681</v>
+        <v>302.7649021905291</v>
       </c>
       <c r="D26">
-        <v>301.2460386760062</v>
+        <v>300.9769705412981</v>
       </c>
       <c r="E26">
-        <v>96.53931221366254</v>
+        <v>100.6637949476933</v>
       </c>
       <c r="F26">
-        <v>98.98758561673814</v>
+        <v>103.1120683507689</v>
       </c>
       <c r="G26">
         <v>104.9</v>
@@ -3425,28 +3425,28 @@
         <v>36.717</v>
       </c>
       <c r="M26">
-        <v>5.375025898988882</v>
+        <v>5.598985311446752</v>
       </c>
       <c r="N26">
-        <v>31.34197410101112</v>
+        <v>31.11801468855325</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>31.34197410101112</v>
+        <v>31.11801468855325</v>
       </c>
       <c r="Q26">
-        <v>32.10597410101112</v>
+        <v>31.88201468855324</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07444995237619192</v>
+        <v>0.07483195174120781</v>
       </c>
       <c r="T26">
-        <v>0.5584408979402958</v>
+        <v>0.5658867765794997</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.831036852660931</v>
+        <v>6.557795378554493</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06969896380590586</v>
+        <v>0.06978396380590586</v>
       </c>
       <c r="C27">
-        <v>302.7649021905291</v>
+        <v>298.3718315475534</v>
       </c>
       <c r="D27">
-        <v>300.9769705412981</v>
+        <v>300.7083826323531</v>
       </c>
       <c r="E27">
-        <v>100.6637949476933</v>
+        <v>104.7882776817241</v>
       </c>
       <c r="F27">
-        <v>103.1120683507689</v>
+        <v>107.2365510847997</v>
       </c>
       <c r="G27">
         <v>104.9</v>
@@ -3507,28 +3507,28 @@
         <v>36.717</v>
       </c>
       <c r="M27">
-        <v>5.598985311446752</v>
+        <v>5.822944723904622</v>
       </c>
       <c r="N27">
-        <v>31.11801468855325</v>
+        <v>30.89405527609538</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>31.11801468855325</v>
+        <v>30.89405527609538</v>
       </c>
       <c r="Q27">
-        <v>31.88201468855324</v>
+        <v>31.65805527609538</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07483195174120781</v>
+        <v>0.07522427541338629</v>
       </c>
       <c r="T27">
-        <v>0.5658867765794997</v>
+        <v>0.5735338951819253</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.557795378554493</v>
+        <v>6.30557247937932</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06978396380590586</v>
+        <v>0.07013896380590587</v>
       </c>
       <c r="C28">
-        <v>298.3718315475534</v>
+        <v>293.1307618963846</v>
       </c>
       <c r="D28">
-        <v>300.7083826323531</v>
+        <v>299.5917957152151</v>
       </c>
       <c r="E28">
-        <v>104.7882776817241</v>
+        <v>108.9127604157548</v>
       </c>
       <c r="F28">
-        <v>107.2365510847997</v>
+        <v>111.3610338188304</v>
       </c>
       <c r="G28">
         <v>104.9</v>
@@ -3589,45 +3589,45 @@
         <v>36.717</v>
       </c>
       <c r="M28">
-        <v>5.822944723904622</v>
+        <v>6.158265170181322</v>
       </c>
       <c r="N28">
-        <v>30.89405527609538</v>
+        <v>30.55873482981868</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>30.89405527609538</v>
+        <v>30.55873482981868</v>
       </c>
       <c r="Q28">
-        <v>31.65805527609538</v>
+        <v>31.32273482981867</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07522427541338629</v>
+        <v>0.0756273476793231</v>
       </c>
       <c r="T28">
-        <v>0.5735338951819253</v>
+        <v>0.5813905238830477</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.30557247937932</v>
+        <v>5.962231080562403</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07013896380590587</v>
+        <v>0.07023396380590585</v>
       </c>
       <c r="C29">
-        <v>293.1307618963846</v>
+        <v>288.7088792492311</v>
       </c>
       <c r="D29">
-        <v>299.5917957152151</v>
+        <v>299.2943958020924</v>
       </c>
       <c r="E29">
-        <v>108.9127604157548</v>
+        <v>113.0372431497856</v>
       </c>
       <c r="F29">
-        <v>111.3610338188304</v>
+        <v>115.4855165528612</v>
       </c>
       <c r="G29">
         <v>104.9</v>
@@ -3671,28 +3671,28 @@
         <v>36.717</v>
       </c>
       <c r="M29">
-        <v>6.158265170181322</v>
+        <v>6.386349065373223</v>
       </c>
       <c r="N29">
-        <v>30.55873482981868</v>
+        <v>30.33065093462677</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>30.55873482981868</v>
+        <v>30.33065093462677</v>
       </c>
       <c r="Q29">
-        <v>31.32273482981867</v>
+        <v>31.09465093462677</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0756273476793231</v>
+        <v>0.07604161639709146</v>
       </c>
       <c r="T29">
-        <v>0.5813905238830477</v>
+        <v>0.5894653922703121</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.962231080562403</v>
+        <v>5.749294256256603</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07023396380590585</v>
+        <v>0.07032896380590586</v>
       </c>
       <c r="C30">
-        <v>288.7088792492311</v>
+        <v>284.2875864646643</v>
       </c>
       <c r="D30">
-        <v>299.2943958020924</v>
+        <v>298.9975857515562</v>
       </c>
       <c r="E30">
-        <v>113.0372431497856</v>
+        <v>117.1617258838163</v>
       </c>
       <c r="F30">
-        <v>115.4855165528612</v>
+        <v>119.6099992868919</v>
       </c>
       <c r="G30">
         <v>104.9</v>
@@ -3753,28 +3753,28 @@
         <v>36.717</v>
       </c>
       <c r="M30">
-        <v>6.386349065373223</v>
+        <v>6.614432960565125</v>
       </c>
       <c r="N30">
-        <v>30.33065093462677</v>
+        <v>30.10256703943487</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>30.33065093462677</v>
+        <v>30.10256703943487</v>
       </c>
       <c r="Q30">
-        <v>31.09465093462677</v>
+        <v>30.86656703943487</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07604161639709146</v>
+        <v>0.07646755465620544</v>
       </c>
       <c r="T30">
-        <v>0.5894653922703121</v>
+        <v>0.5977677217389082</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.749294256256603</v>
+        <v>5.551042730178788</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07032896380590585</v>
+        <v>0.07042396380590586</v>
       </c>
       <c r="C31">
-        <v>284.2875864646643</v>
+        <v>279.8668817895237</v>
       </c>
       <c r="D31">
-        <v>298.9975857515562</v>
+        <v>298.7013638104464</v>
       </c>
       <c r="E31">
-        <v>117.1617258838163</v>
+        <v>121.2862086178471</v>
       </c>
       <c r="F31">
-        <v>119.6099992868919</v>
+        <v>123.7344820209227</v>
       </c>
       <c r="G31">
         <v>104.9</v>
@@ -3835,28 +3835,28 @@
         <v>36.717</v>
       </c>
       <c r="M31">
-        <v>6.614432960565123</v>
+        <v>6.842516855757025</v>
       </c>
       <c r="N31">
-        <v>30.10256703943487</v>
+        <v>29.87448314424297</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>30.10256703943487</v>
+        <v>29.87448314424297</v>
       </c>
       <c r="Q31">
-        <v>30.86656703943487</v>
+        <v>30.63848314424297</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07646755465620543</v>
+        <v>0.07690566257986552</v>
       </c>
       <c r="T31">
-        <v>0.5977677217389081</v>
+        <v>0.6063072606208926</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.55104273017879</v>
+        <v>5.366007972506162</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07042396380590586</v>
+        <v>0.07051896380590586</v>
       </c>
       <c r="C32">
-        <v>279.8668817895237</v>
+        <v>275.4467634775899</v>
       </c>
       <c r="D32">
-        <v>298.7013638104464</v>
+        <v>298.4057282325433</v>
       </c>
       <c r="E32">
-        <v>121.2862086178471</v>
+        <v>125.4106913518778</v>
       </c>
       <c r="F32">
-        <v>123.7344820209227</v>
+        <v>127.8589647549534</v>
       </c>
       <c r="G32">
         <v>104.9</v>
@@ -3917,28 +3917,28 @@
         <v>36.717</v>
       </c>
       <c r="M32">
-        <v>6.842516855757025</v>
+        <v>7.070600750948926</v>
       </c>
       <c r="N32">
-        <v>29.87448314424297</v>
+        <v>29.64639924905107</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>29.87448314424297</v>
+        <v>29.64639924905107</v>
       </c>
       <c r="Q32">
-        <v>30.63848314424297</v>
+        <v>30.41039924905107</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07690566257986552</v>
+        <v>0.07735646928392154</v>
       </c>
       <c r="T32">
-        <v>0.6063072606208926</v>
+        <v>0.6150943223690214</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.366007972506162</v>
+        <v>5.192910941134996</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07051896380590586</v>
+        <v>0.07061396380590586</v>
       </c>
       <c r="C33">
-        <v>275.4467634775899</v>
+        <v>271.0272297895491</v>
       </c>
       <c r="D33">
-        <v>298.4057282325433</v>
+        <v>298.1106772785333</v>
       </c>
       <c r="E33">
-        <v>125.4106913518778</v>
+        <v>129.5351740859086</v>
       </c>
       <c r="F33">
-        <v>127.8589647549534</v>
+        <v>131.9834474889842</v>
       </c>
       <c r="G33">
         <v>104.9</v>
@@ -3999,28 +3999,28 @@
         <v>36.717</v>
       </c>
       <c r="M33">
-        <v>7.070600750948926</v>
+        <v>7.298684646140827</v>
       </c>
       <c r="N33">
-        <v>29.64639924905107</v>
+        <v>29.41831535385917</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>29.64639924905107</v>
+        <v>29.41831535385917</v>
       </c>
       <c r="Q33">
-        <v>30.41039924905107</v>
+        <v>30.18231535385917</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07735646928392154</v>
+        <v>0.07782053500868509</v>
       </c>
       <c r="T33">
-        <v>0.6150943223690214</v>
+        <v>0.6241398271097424</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.192910941134996</v>
+        <v>5.030632474224528</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07061396380590586</v>
+        <v>0.07070896380590586</v>
       </c>
       <c r="C34">
-        <v>271.0272297895491</v>
+        <v>266.6082789929604</v>
       </c>
       <c r="D34">
-        <v>298.1106772785333</v>
+        <v>297.8162092159753</v>
       </c>
       <c r="E34">
-        <v>129.5351740859086</v>
+        <v>133.6596568199394</v>
       </c>
       <c r="F34">
-        <v>131.9834474889842</v>
+        <v>136.107930223015</v>
       </c>
       <c r="G34">
         <v>104.9</v>
@@ -4081,28 +4081,28 @@
         <v>36.717</v>
       </c>
       <c r="M34">
-        <v>7.298684646140827</v>
+        <v>7.526768541332728</v>
       </c>
       <c r="N34">
-        <v>29.41831535385917</v>
+        <v>29.19023145866727</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>29.41831535385917</v>
+        <v>29.19023145866727</v>
       </c>
       <c r="Q34">
-        <v>30.18231535385917</v>
+        <v>29.95423145866727</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07782053500868509</v>
+        <v>0.07829845344165054</v>
       </c>
       <c r="T34">
-        <v>0.6241398271097424</v>
+        <v>0.6334553469173505</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.030632474224528</v>
+        <v>4.878189065914693</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07070896380590586</v>
+        <v>0.07080396380590585</v>
       </c>
       <c r="C35">
-        <v>266.6082789929604</v>
+        <v>262.189909362221</v>
       </c>
       <c r="D35">
-        <v>297.8162092159753</v>
+        <v>297.5223223192668</v>
       </c>
       <c r="E35">
-        <v>133.6596568199394</v>
+        <v>137.7841395539701</v>
       </c>
       <c r="F35">
-        <v>136.107930223015</v>
+        <v>140.2324129570457</v>
       </c>
       <c r="G35">
         <v>104.9</v>
@@ -4163,28 +4163,28 @@
         <v>36.717</v>
       </c>
       <c r="M35">
-        <v>7.526768541332728</v>
+        <v>7.754852436524629</v>
       </c>
       <c r="N35">
-        <v>29.19023145866727</v>
+        <v>28.96214756347537</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>29.19023145866727</v>
+        <v>28.96214756347537</v>
       </c>
       <c r="Q35">
-        <v>29.95423145866727</v>
+        <v>29.72614756347537</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07829845344165054</v>
+        <v>0.07879085425137251</v>
       </c>
       <c r="T35">
-        <v>0.6334553469173505</v>
+        <v>0.6430531552039769</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.878189065914693</v>
+        <v>4.734712916917202</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07080396380590585</v>
+        <v>0.07089896380590585</v>
       </c>
       <c r="C36">
-        <v>262.189909362221</v>
+        <v>257.7721191785329</v>
       </c>
       <c r="D36">
-        <v>297.5223223192668</v>
+        <v>297.2290148696094</v>
       </c>
       <c r="E36">
-        <v>137.7841395539701</v>
+        <v>141.9086222880009</v>
       </c>
       <c r="F36">
-        <v>140.2324129570457</v>
+        <v>144.3568956910765</v>
       </c>
       <c r="G36">
         <v>104.9</v>
@@ -4245,28 +4245,28 @@
         <v>36.717</v>
       </c>
       <c r="M36">
-        <v>7.754852436524629</v>
+        <v>7.98293633171653</v>
       </c>
       <c r="N36">
-        <v>28.96214756347537</v>
+        <v>28.73406366828347</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>28.96214756347537</v>
+        <v>28.73406366828347</v>
       </c>
       <c r="Q36">
-        <v>29.72614756347537</v>
+        <v>29.49806366828347</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07879085425137251</v>
+        <v>0.07929840585523978</v>
       </c>
       <c r="T36">
-        <v>0.6430531552039769</v>
+        <v>0.6529462806686536</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.734712916917202</v>
+        <v>4.599435405005282</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07089896380590585</v>
+        <v>0.07189396380590586</v>
       </c>
       <c r="C37">
-        <v>257.7721191785329</v>
+        <v>250.6100196587333</v>
       </c>
       <c r="D37">
-        <v>297.2290148696094</v>
+        <v>294.1913980838405</v>
       </c>
       <c r="E37">
-        <v>141.9086222880009</v>
+        <v>146.0331050220316</v>
       </c>
       <c r="F37">
-        <v>144.3568956910765</v>
+        <v>148.4813784251072</v>
       </c>
       <c r="G37">
         <v>104.9</v>
@@ -4327,45 +4327,45 @@
         <v>36.717</v>
       </c>
       <c r="M37">
-        <v>7.98293633171653</v>
+        <v>8.5822236729712</v>
       </c>
       <c r="N37">
-        <v>28.73406366828347</v>
+        <v>28.1347763270288</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>28.73406366828347</v>
+        <v>28.1347763270288</v>
       </c>
       <c r="Q37">
-        <v>29.49806366828347</v>
+        <v>28.8987763270288</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07929840585523978</v>
+        <v>0.07982181844672791</v>
       </c>
       <c r="T37">
-        <v>0.6529462806686536</v>
+        <v>0.6631485663041012</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.599435405005282</v>
+        <v>4.278261835057537</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07189396380590586</v>
+        <v>0.07201396380590586</v>
       </c>
       <c r="C38">
-        <v>250.6100196587333</v>
+        <v>246.1233815265286</v>
       </c>
       <c r="D38">
-        <v>294.1913980838405</v>
+        <v>293.8292426856666</v>
       </c>
       <c r="E38">
-        <v>146.0331050220316</v>
+        <v>150.1575877560624</v>
       </c>
       <c r="F38">
-        <v>148.4813784251072</v>
+        <v>152.605861159138</v>
       </c>
       <c r="G38">
         <v>104.9</v>
@@ -4409,28 +4409,28 @@
         <v>36.717</v>
       </c>
       <c r="M38">
-        <v>8.582223672971198</v>
+        <v>8.820618774998175</v>
       </c>
       <c r="N38">
-        <v>28.1347763270288</v>
+        <v>27.89638122500183</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>28.1347763270288</v>
+        <v>27.89638122500183</v>
       </c>
       <c r="Q38">
-        <v>28.8987763270288</v>
+        <v>28.66038122500182</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07982181844672791</v>
+        <v>0.08036184731096169</v>
       </c>
       <c r="T38">
-        <v>0.6631485663041012</v>
+        <v>0.673674734023214</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.278261835057538</v>
+        <v>4.16263313681274</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07201396380590586</v>
+        <v>0.07213396380590585</v>
       </c>
       <c r="C39">
-        <v>246.1233815265286</v>
+        <v>241.6376339388845</v>
       </c>
       <c r="D39">
-        <v>293.8292426856666</v>
+        <v>293.4679778320532</v>
       </c>
       <c r="E39">
-        <v>150.1575877560624</v>
+        <v>154.2820704900931</v>
       </c>
       <c r="F39">
-        <v>152.605861159138</v>
+        <v>156.7303438931687</v>
       </c>
       <c r="G39">
         <v>104.9</v>
@@ -4491,28 +4491,28 @@
         <v>36.717</v>
       </c>
       <c r="M39">
-        <v>8.820618774998175</v>
+        <v>9.059013877025153</v>
       </c>
       <c r="N39">
-        <v>27.89638122500183</v>
+        <v>27.65798612297485</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>27.89638122500183</v>
+        <v>27.65798612297485</v>
       </c>
       <c r="Q39">
-        <v>28.66038122500182</v>
+        <v>28.42198612297485</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08036184731096169</v>
+        <v>0.08091929646113848</v>
       </c>
       <c r="T39">
-        <v>0.673674734023214</v>
+        <v>0.6845404555397173</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.16263313681274</v>
+        <v>4.053090159528194</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07213396380590585</v>
+        <v>0.07361896380590587</v>
       </c>
       <c r="C40">
-        <v>241.6376339388845</v>
+        <v>233.1149151066006</v>
       </c>
       <c r="D40">
-        <v>293.4679778320532</v>
+        <v>289.0697417338001</v>
       </c>
       <c r="E40">
-        <v>154.2820704900931</v>
+        <v>158.4065532241239</v>
       </c>
       <c r="F40">
-        <v>156.7303438931687</v>
+        <v>160.8548266271995</v>
       </c>
       <c r="G40">
         <v>104.9</v>
@@ -4573,45 +4573,45 @@
         <v>36.717</v>
       </c>
       <c r="M40">
-        <v>9.059013877025153</v>
+        <v>9.860400872247331</v>
       </c>
       <c r="N40">
-        <v>27.65798612297485</v>
+        <v>26.85659912775267</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>27.65798612297485</v>
+        <v>26.85659912775267</v>
       </c>
       <c r="Q40">
-        <v>28.42198612297485</v>
+        <v>27.62059912775267</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08091929646113848</v>
+        <v>0.08149502263263256</v>
       </c>
       <c r="T40">
-        <v>0.6845404555397173</v>
+        <v>0.6957624302206964</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.053090159528194</v>
+        <v>3.723682279829223</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07361896380590587</v>
+        <v>0.07377396380590587</v>
       </c>
       <c r="C41">
-        <v>233.1149151066006</v>
+        <v>228.5389437014501</v>
       </c>
       <c r="D41">
-        <v>289.0697417338001</v>
+        <v>288.6182530626804</v>
       </c>
       <c r="E41">
-        <v>158.4065532241239</v>
+        <v>162.5310359581547</v>
       </c>
       <c r="F41">
-        <v>160.8548266271995</v>
+        <v>164.9793093612303</v>
       </c>
       <c r="G41">
         <v>104.9</v>
@@ -4655,28 +4655,28 @@
         <v>36.717</v>
       </c>
       <c r="M41">
-        <v>9.860400872247331</v>
+        <v>10.11323166384341</v>
       </c>
       <c r="N41">
-        <v>26.85659912775267</v>
+        <v>26.60376833615658</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>26.85659912775267</v>
+        <v>26.60376833615658</v>
       </c>
       <c r="Q41">
-        <v>27.62059912775267</v>
+        <v>27.36776833615658</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08149502263263256</v>
+        <v>0.08208993967650977</v>
       </c>
       <c r="T41">
-        <v>0.6957624302206964</v>
+        <v>0.7073584707243746</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.723682279829223</v>
+        <v>3.630590222833493</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07377396380590587</v>
+        <v>0.07392896380590586</v>
       </c>
       <c r="C42">
-        <v>228.5389437014501</v>
+        <v>223.9643804280618</v>
       </c>
       <c r="D42">
-        <v>288.6182530626804</v>
+        <v>288.1681725233228</v>
       </c>
       <c r="E42">
-        <v>162.5310359581547</v>
+        <v>166.6555186921854</v>
       </c>
       <c r="F42">
-        <v>164.9793093612303</v>
+        <v>169.103792095261</v>
       </c>
       <c r="G42">
         <v>104.9</v>
@@ -4737,28 +4737,28 @@
         <v>36.717</v>
       </c>
       <c r="M42">
-        <v>10.11323166384341</v>
+        <v>10.3660624554395</v>
       </c>
       <c r="N42">
-        <v>26.60376833615658</v>
+        <v>26.3509375445605</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>26.60376833615658</v>
+        <v>26.3509375445605</v>
       </c>
       <c r="Q42">
-        <v>27.36776833615658</v>
+        <v>27.1149375445605</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08208993967650977</v>
+        <v>0.08270502339984043</v>
       </c>
       <c r="T42">
-        <v>0.7073584707243746</v>
+        <v>0.7193475973468216</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.630590222833493</v>
+        <v>3.542039241788773</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07392896380590586</v>
+        <v>0.07525996380590586</v>
       </c>
       <c r="C43">
-        <v>223.9643804280618</v>
+        <v>216.0320306941609</v>
       </c>
       <c r="D43">
-        <v>288.1681725233228</v>
+        <v>284.3603055234527</v>
       </c>
       <c r="E43">
-        <v>166.6555186921854</v>
+        <v>170.7800014262162</v>
       </c>
       <c r="F43">
-        <v>169.103792095261</v>
+        <v>173.2282748292918</v>
       </c>
       <c r="G43">
         <v>104.9</v>
@@ -4819,45 +4819,45 @@
         <v>36.717</v>
       </c>
       <c r="M43">
-        <v>10.3660624554395</v>
+        <v>11.1039324165576</v>
       </c>
       <c r="N43">
-        <v>26.3509375445605</v>
+        <v>25.61306758344239</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>26.3509375445605</v>
+        <v>25.61306758344239</v>
       </c>
       <c r="Q43">
-        <v>27.1149375445605</v>
+        <v>26.37706758344239</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08270502339984043</v>
+        <v>0.08334131690673424</v>
       </c>
       <c r="T43">
-        <v>0.7193475973468216</v>
+        <v>0.7317501421286635</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.542039241788773</v>
+        <v>3.306666379313469</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07525996380590587</v>
+        <v>0.07544296380590586</v>
       </c>
       <c r="C44">
-        <v>216.0320306941609</v>
+        <v>211.3918570791782</v>
       </c>
       <c r="D44">
-        <v>284.3603055234526</v>
+        <v>283.8446146425007</v>
       </c>
       <c r="E44">
-        <v>170.7800014262162</v>
+        <v>174.9044841602469</v>
       </c>
       <c r="F44">
-        <v>173.2282748292918</v>
+        <v>177.3527575633225</v>
       </c>
       <c r="G44">
         <v>104.9</v>
@@ -4901,28 +4901,28 @@
         <v>36.717</v>
       </c>
       <c r="M44">
-        <v>11.1039324165576</v>
+        <v>11.36831175980897</v>
       </c>
       <c r="N44">
-        <v>25.61306758344239</v>
+        <v>25.34868824019102</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>25.61306758344239</v>
+        <v>25.34868824019102</v>
       </c>
       <c r="Q44">
-        <v>26.37706758344239</v>
+        <v>26.11268824019102</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08334131690673424</v>
+        <v>0.08399993650158923</v>
       </c>
       <c r="T44">
-        <v>0.7317501421286634</v>
+        <v>0.7445878639203943</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.30666637931347</v>
+        <v>3.229767161189901</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07544296380590586</v>
+        <v>0.07562596380590587</v>
       </c>
       <c r="C45">
-        <v>211.3918570791782</v>
+        <v>206.7535505016998</v>
       </c>
       <c r="D45">
-        <v>283.8446146425007</v>
+        <v>283.3307907990531</v>
       </c>
       <c r="E45">
-        <v>174.9044841602469</v>
+        <v>179.0289668942777</v>
       </c>
       <c r="F45">
-        <v>177.3527575633225</v>
+        <v>181.4772402973533</v>
       </c>
       <c r="G45">
         <v>104.9</v>
@@ -4983,28 +4983,28 @@
         <v>36.717</v>
       </c>
       <c r="M45">
-        <v>11.36831175980897</v>
+        <v>11.63269110306035</v>
       </c>
       <c r="N45">
-        <v>25.34868824019102</v>
+        <v>25.08430889693965</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>25.34868824019102</v>
+        <v>25.08430889693965</v>
       </c>
       <c r="Q45">
-        <v>26.11268824019102</v>
+        <v>25.84830889693965</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08399993650158923</v>
+        <v>0.0846820782248319</v>
       </c>
       <c r="T45">
-        <v>0.7445878639203943</v>
+        <v>0.7578840757761156</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.229767161189901</v>
+        <v>3.156363362071949</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07562596380590587</v>
+        <v>0.07580896380590585</v>
       </c>
       <c r="C46">
-        <v>206.7535505016998</v>
+        <v>202.1171008407491</v>
       </c>
       <c r="D46">
-        <v>283.3307907990531</v>
+        <v>282.8188238721332</v>
       </c>
       <c r="E46">
-        <v>179.0289668942777</v>
+        <v>183.1534496283084</v>
       </c>
       <c r="F46">
-        <v>181.4772402973533</v>
+        <v>185.601723031384</v>
       </c>
       <c r="G46">
         <v>104.9</v>
@@ -5065,28 +5065,28 @@
         <v>36.717</v>
       </c>
       <c r="M46">
-        <v>11.63269110306035</v>
+        <v>11.89707044631172</v>
       </c>
       <c r="N46">
-        <v>25.08430889693965</v>
+        <v>24.81992955368828</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>25.08430889693965</v>
+        <v>24.81992955368828</v>
       </c>
       <c r="Q46">
-        <v>25.84830889693965</v>
+        <v>25.58392955368828</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0846820782248319</v>
+        <v>0.085389025101647</v>
       </c>
       <c r="T46">
-        <v>0.7578840757761156</v>
+        <v>0.7716637862447723</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.156363362071949</v>
+        <v>3.086221954025905</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07580896380590585</v>
+        <v>0.07599196380590587</v>
       </c>
       <c r="C47">
-        <v>202.1171008407491</v>
+        <v>197.48249804837</v>
       </c>
       <c r="D47">
-        <v>282.8188238721332</v>
+        <v>282.3087038137848</v>
       </c>
       <c r="E47">
-        <v>183.1534496283084</v>
+        <v>187.2779323623392</v>
       </c>
       <c r="F47">
-        <v>185.601723031384</v>
+        <v>189.7262057654148</v>
       </c>
       <c r="G47">
         <v>104.9</v>
@@ -5147,28 +5147,28 @@
         <v>36.717</v>
       </c>
       <c r="M47">
-        <v>11.89707044631172</v>
+        <v>12.16144978956309</v>
       </c>
       <c r="N47">
-        <v>24.81992955368828</v>
+        <v>24.55555021043691</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>24.81992955368828</v>
+        <v>24.55555021043691</v>
       </c>
       <c r="Q47">
-        <v>25.58392955368828</v>
+        <v>25.31955021043691</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.085389025101647</v>
+        <v>0.08612215519612196</v>
       </c>
       <c r="T47">
-        <v>0.7716637862447723</v>
+        <v>0.7859538563604163</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.086221954025905</v>
+        <v>3.019130172416647</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07599196380590587</v>
+        <v>0.07984096380590587</v>
       </c>
       <c r="C48">
-        <v>197.48249804837</v>
+        <v>183.0395701575874</v>
       </c>
       <c r="D48">
-        <v>282.3087038137848</v>
+        <v>271.9902586570329</v>
       </c>
       <c r="E48">
-        <v>187.2779323623392</v>
+        <v>191.40241509637</v>
       </c>
       <c r="F48">
-        <v>189.7262057654148</v>
+        <v>193.8506884994456</v>
       </c>
       <c r="G48">
         <v>104.9</v>
@@ -5229,45 +5229,45 @@
         <v>36.717</v>
       </c>
       <c r="M48">
-        <v>12.16144978956309</v>
+        <v>13.93786450311014</v>
       </c>
       <c r="N48">
-        <v>24.55555021043691</v>
+        <v>22.77913549688986</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>24.55555021043691</v>
+        <v>22.77913549688986</v>
       </c>
       <c r="Q48">
-        <v>25.31955021043691</v>
+        <v>23.54313549688986</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08612215519612196</v>
+        <v>0.08688295057718087</v>
       </c>
       <c r="T48">
-        <v>0.7859538563604163</v>
+        <v>0.8007831744049524</v>
       </c>
       <c r="U48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.019130172416647</v>
+        <v>2.63433469250665</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07984096380590587</v>
+        <v>0.08010196380590587</v>
       </c>
       <c r="C49">
-        <v>183.0395701575874</v>
+        <v>178.2426360469502</v>
       </c>
       <c r="D49">
-        <v>271.9902586570329</v>
+        <v>271.3178072804266</v>
       </c>
       <c r="E49">
-        <v>191.40241509637</v>
+        <v>195.5268978304007</v>
       </c>
       <c r="F49">
-        <v>193.8506884994456</v>
+        <v>197.9751712334763</v>
       </c>
       <c r="G49">
         <v>104.9</v>
@@ -5311,28 +5311,28 @@
         <v>36.717</v>
       </c>
       <c r="M49">
-        <v>13.93786450311014</v>
+        <v>14.23441481168695</v>
       </c>
       <c r="N49">
-        <v>22.77913549688986</v>
+        <v>22.48258518831305</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>22.77913549688986</v>
+        <v>22.48258518831305</v>
       </c>
       <c r="Q49">
-        <v>23.54313549688986</v>
+        <v>23.24658518831305</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08688295057718087</v>
+        <v>0.08767300731904973</v>
       </c>
       <c r="T49">
-        <v>0.8007831744049524</v>
+        <v>0.8161828508358169</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.63433469250665</v>
+        <v>2.579452719746095</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08010196380590587</v>
+        <v>0.08036296380590587</v>
       </c>
       <c r="C50">
-        <v>178.2426360469503</v>
+        <v>173.4490187877729</v>
       </c>
       <c r="D50">
-        <v>271.3178072804266</v>
+        <v>270.64867275528</v>
       </c>
       <c r="E50">
-        <v>195.5268978304007</v>
+        <v>199.6513805644315</v>
       </c>
       <c r="F50">
-        <v>197.9751712334763</v>
+        <v>202.0996539675071</v>
       </c>
       <c r="G50">
         <v>104.9</v>
@@ -5393,28 +5393,28 @@
         <v>36.717</v>
       </c>
       <c r="M50">
-        <v>14.23441481168695</v>
+        <v>14.53096512026376</v>
       </c>
       <c r="N50">
-        <v>22.48258518831305</v>
+        <v>22.18603487973624</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>22.48258518831305</v>
+        <v>22.18603487973624</v>
       </c>
       <c r="Q50">
-        <v>23.24658518831305</v>
+        <v>22.95003487973624</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08767300731904973</v>
+        <v>0.08849404667824678</v>
       </c>
       <c r="T50">
-        <v>0.8161828508358168</v>
+        <v>0.832186436146323</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.579452719746095</v>
+        <v>2.526810827506379</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08036296380590587</v>
+        <v>0.08257396380590587</v>
       </c>
       <c r="C51">
-        <v>173.4490187877729</v>
+        <v>163.7858160923816</v>
       </c>
       <c r="D51">
-        <v>270.64867275528</v>
+        <v>265.1099527939194</v>
       </c>
       <c r="E51">
-        <v>199.6513805644315</v>
+        <v>203.7758632984622</v>
       </c>
       <c r="F51">
-        <v>202.0996539675071</v>
+        <v>206.2241367015378</v>
       </c>
       <c r="G51">
         <v>104.9</v>
@@ -5475,45 +5475,45 @@
         <v>36.717</v>
       </c>
       <c r="M51">
-        <v>14.53096512026376</v>
+        <v>15.63178956197657</v>
       </c>
       <c r="N51">
-        <v>22.18603487973624</v>
+        <v>21.08521043802343</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>22.18603487973624</v>
+        <v>21.08521043802343</v>
       </c>
       <c r="Q51">
-        <v>22.95003487973624</v>
+        <v>21.84921043802343</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08849404667824678</v>
+        <v>0.08934792761181172</v>
       </c>
       <c r="T51">
-        <v>0.832186436146323</v>
+        <v>0.8488301648692496</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.526810827506379</v>
+        <v>2.348867342054809</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08257396380590587</v>
+        <v>0.08287396380590586</v>
       </c>
       <c r="C52">
-        <v>163.7858160923816</v>
+        <v>158.9272290098599</v>
       </c>
       <c r="D52">
-        <v>265.1099527939194</v>
+        <v>264.3758484454285</v>
       </c>
       <c r="E52">
-        <v>203.7758632984622</v>
+        <v>207.900346032493</v>
       </c>
       <c r="F52">
-        <v>206.2241367015378</v>
+        <v>210.3486194355686</v>
       </c>
       <c r="G52">
         <v>104.9</v>
@@ -5557,28 +5557,28 @@
         <v>36.717</v>
       </c>
       <c r="M52">
-        <v>15.63178956197657</v>
+        <v>15.9444253532161</v>
       </c>
       <c r="N52">
-        <v>21.08521043802343</v>
+        <v>20.7725746467839</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>21.08521043802343</v>
+        <v>20.7725746467839</v>
       </c>
       <c r="Q52">
-        <v>21.84921043802343</v>
+        <v>21.5365746467839</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08934792761181172</v>
+        <v>0.09023666082837931</v>
       </c>
       <c r="T52">
-        <v>0.8488301648692496</v>
+        <v>0.8661532294584179</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.348867342054809</v>
+        <v>2.302811119661577</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08287396380590586</v>
+        <v>0.08317396380590586</v>
       </c>
       <c r="C53">
-        <v>158.9272290098599</v>
+        <v>154.0726962530227</v>
       </c>
       <c r="D53">
-        <v>264.3758484454285</v>
+        <v>263.6457984226221</v>
       </c>
       <c r="E53">
-        <v>207.900346032493</v>
+        <v>212.0248287665237</v>
       </c>
       <c r="F53">
-        <v>210.3486194355686</v>
+        <v>214.4731021695993</v>
       </c>
       <c r="G53">
         <v>104.9</v>
@@ -5639,28 +5639,28 @@
         <v>36.717</v>
       </c>
       <c r="M53">
-        <v>15.9444253532161</v>
+        <v>16.25706114445563</v>
       </c>
       <c r="N53">
-        <v>20.7725746467839</v>
+        <v>20.45993885554437</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>20.7725746467839</v>
+        <v>20.45993885554437</v>
       </c>
       <c r="Q53">
-        <v>21.5365746467839</v>
+        <v>21.22393885554437</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09023666082837931</v>
+        <v>0.0911624245956372</v>
       </c>
       <c r="T53">
-        <v>0.8661532294584179</v>
+        <v>0.8841980884054683</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.302811119661577</v>
+        <v>2.258526290437316</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08317396380590586</v>
+        <v>0.08347396380590587</v>
       </c>
       <c r="C54">
-        <v>154.0726962530227</v>
+        <v>149.2221843273996</v>
       </c>
       <c r="D54">
-        <v>263.6457984226221</v>
+        <v>262.9197692310297</v>
       </c>
       <c r="E54">
-        <v>212.0248287665237</v>
+        <v>216.1493115005545</v>
       </c>
       <c r="F54">
-        <v>214.4731021695993</v>
+        <v>218.5975849036301</v>
       </c>
       <c r="G54">
         <v>104.9</v>
@@ -5721,28 +5721,28 @@
         <v>36.717</v>
       </c>
       <c r="M54">
-        <v>16.25706114445563</v>
+        <v>16.56969693569516</v>
       </c>
       <c r="N54">
-        <v>20.45993885554437</v>
+        <v>20.14730306430484</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>20.45993885554437</v>
+        <v>20.14730306430484</v>
       </c>
       <c r="Q54">
-        <v>21.22393885554437</v>
+        <v>20.91130306430484</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0911624245956372</v>
+        <v>0.09212758256575715</v>
       </c>
       <c r="T54">
-        <v>0.8841980884054683</v>
+        <v>0.903010813690691</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.258526290437316</v>
+        <v>2.215912586844158</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08347396380590587</v>
+        <v>0.08377396380590585</v>
       </c>
       <c r="C55">
-        <v>149.2221843273996</v>
+        <v>144.375660106456</v>
       </c>
       <c r="D55">
-        <v>262.9197692310297</v>
+        <v>262.1977277441168</v>
       </c>
       <c r="E55">
-        <v>216.1493115005545</v>
+        <v>220.2737942345852</v>
       </c>
       <c r="F55">
-        <v>218.5975849036301</v>
+        <v>222.7220676376608</v>
       </c>
       <c r="G55">
         <v>104.9</v>
@@ -5803,28 +5803,28 @@
         <v>36.717</v>
       </c>
       <c r="M55">
-        <v>16.56969693569516</v>
+        <v>16.88233272693469</v>
       </c>
       <c r="N55">
-        <v>20.14730306430484</v>
+        <v>19.83466727306531</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>20.14730306430484</v>
+        <v>19.83466727306531</v>
       </c>
       <c r="Q55">
-        <v>20.91130306430484</v>
+        <v>20.59866727306531</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09212758256575715</v>
+        <v>0.0931347039258823</v>
       </c>
       <c r="T55">
-        <v>0.903010813690691</v>
+        <v>0.922641483553532</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.215912586844158</v>
+        <v>2.174877168569267</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08377396380590585</v>
+        <v>0.08407396380590586</v>
       </c>
       <c r="C56">
-        <v>144.375660106456</v>
+        <v>139.5330908265546</v>
       </c>
       <c r="D56">
-        <v>262.1977277441168</v>
+        <v>261.4796411982462</v>
       </c>
       <c r="E56">
-        <v>220.2737942345852</v>
+        <v>224.398276968616</v>
       </c>
       <c r="F56">
-        <v>222.7220676376608</v>
+        <v>226.8465503716916</v>
       </c>
       <c r="G56">
         <v>104.9</v>
@@ -5885,28 +5885,28 @@
         <v>36.717</v>
       </c>
       <c r="M56">
-        <v>16.88233272693469</v>
+        <v>17.19496851817422</v>
       </c>
       <c r="N56">
-        <v>19.83466727306531</v>
+        <v>19.52203148182577</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>19.83466727306531</v>
+        <v>19.52203148182577</v>
       </c>
       <c r="Q56">
-        <v>20.59866727306531</v>
+        <v>20.28603148182577</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.0931347039258823</v>
+        <v>0.09418658623534636</v>
       </c>
       <c r="T56">
-        <v>0.922641483553532</v>
+        <v>0.9431446276324995</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.174877168569267</v>
+        <v>2.135333947322553</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08407396380590586</v>
+        <v>0.08437396380590587</v>
       </c>
       <c r="C57">
-        <v>139.5330908265546</v>
+        <v>134.6944440819996</v>
       </c>
       <c r="D57">
-        <v>261.4796411982462</v>
+        <v>260.765477187722</v>
       </c>
       <c r="E57">
-        <v>224.398276968616</v>
+        <v>228.5227597026468</v>
       </c>
       <c r="F57">
-        <v>226.8465503716916</v>
+        <v>230.9710331057224</v>
       </c>
       <c r="G57">
         <v>104.9</v>
@@ -5967,28 +5967,28 @@
         <v>36.717</v>
       </c>
       <c r="M57">
-        <v>17.19496851817422</v>
+        <v>17.50760430941376</v>
       </c>
       <c r="N57">
-        <v>19.52203148182577</v>
+        <v>19.20939569058624</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>19.52203148182577</v>
+        <v>19.20939569058624</v>
       </c>
       <c r="Q57">
-        <v>20.28603148182577</v>
+        <v>19.97339569058624</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09418658623534636</v>
+        <v>0.09528628137705877</v>
       </c>
       <c r="T57">
-        <v>0.9431446276324995</v>
+        <v>0.9645797328059655</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.135333947322553</v>
+        <v>2.097202983977507</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08437396380590587</v>
+        <v>0.08467396380590586</v>
       </c>
       <c r="C58">
-        <v>134.6944440819996</v>
+        <v>129.8596878201624</v>
       </c>
       <c r="D58">
-        <v>260.765477187722</v>
+        <v>260.0552036599155</v>
       </c>
       <c r="E58">
-        <v>228.5227597026468</v>
+        <v>232.6472424366775</v>
       </c>
       <c r="F58">
-        <v>230.9710331057224</v>
+        <v>235.0955158397531</v>
       </c>
       <c r="G58">
         <v>104.9</v>
@@ -6049,28 +6049,28 @@
         <v>36.717</v>
       </c>
       <c r="M58">
-        <v>17.50760430941376</v>
+        <v>17.82024010065329</v>
       </c>
       <c r="N58">
-        <v>19.20939569058624</v>
+        <v>18.89675989934671</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>19.20939569058624</v>
+        <v>18.89675989934671</v>
       </c>
       <c r="Q58">
-        <v>19.97339569058624</v>
+        <v>19.66075989934671</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09528628137705877</v>
+        <v>0.09643712513001364</v>
       </c>
       <c r="T58">
-        <v>0.9645797328059655</v>
+        <v>0.9870118196154067</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.097202983977507</v>
+        <v>2.060409949170884</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08467396380590586</v>
+        <v>0.08497396380590586</v>
       </c>
       <c r="C59">
-        <v>129.8596878201624</v>
+        <v>125.0287903366855</v>
       </c>
       <c r="D59">
-        <v>260.0552036599155</v>
+        <v>259.3487889104695</v>
       </c>
       <c r="E59">
-        <v>232.6472424366775</v>
+        <v>236.7717251707083</v>
       </c>
       <c r="F59">
-        <v>235.0955158397531</v>
+        <v>239.2199985737839</v>
       </c>
       <c r="G59">
         <v>104.9</v>
@@ -6131,28 +6131,28 @@
         <v>36.717</v>
       </c>
       <c r="M59">
-        <v>17.82024010065329</v>
+        <v>18.13287589189282</v>
       </c>
       <c r="N59">
-        <v>18.89675989934671</v>
+        <v>18.58412410810718</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>18.89675989934671</v>
+        <v>18.58412410810718</v>
       </c>
       <c r="Q59">
-        <v>19.66075989934671</v>
+        <v>19.34812410810718</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09643712513001364</v>
+        <v>0.09764277096644253</v>
       </c>
       <c r="T59">
-        <v>0.9870118196154067</v>
+        <v>1.010512101034821</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.060409949170884</v>
+        <v>2.024885639702421</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08497396380590586</v>
+        <v>0.09365196380590585</v>
       </c>
       <c r="C60">
-        <v>125.0287903366856</v>
+        <v>102.010222048389</v>
       </c>
       <c r="D60">
-        <v>259.3487889104695</v>
+        <v>240.4547033562036</v>
       </c>
       <c r="E60">
-        <v>236.7717251707082</v>
+        <v>240.896207904739</v>
       </c>
       <c r="F60">
-        <v>239.2199985737838</v>
+        <v>243.3444813078146</v>
       </c>
       <c r="G60">
         <v>104.9</v>
@@ -6213,45 +6213,45 @@
         <v>36.717</v>
       </c>
       <c r="M60">
-        <v>18.13287589189282</v>
+        <v>21.90100331770331</v>
       </c>
       <c r="N60">
-        <v>18.58412410810718</v>
+        <v>14.81599668229669</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>18.58412410810718</v>
+        <v>14.81599668229669</v>
       </c>
       <c r="Q60">
-        <v>19.34812410810718</v>
+        <v>15.57999668229668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09764277096644251</v>
+        <v>0.09890722879489233</v>
       </c>
       <c r="T60">
-        <v>1.010512101034821</v>
+        <v>1.035158737645426</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.024885639702421</v>
+        <v>1.676498536042886</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09365196380590585</v>
+        <v>0.09409396380590586</v>
       </c>
       <c r="C61">
-        <v>102.010222048389</v>
+        <v>96.99680628743141</v>
       </c>
       <c r="D61">
-        <v>240.4547033562036</v>
+        <v>239.5657703292768</v>
       </c>
       <c r="E61">
-        <v>240.896207904739</v>
+        <v>245.0206906387698</v>
       </c>
       <c r="F61">
-        <v>243.3444813078146</v>
+        <v>247.4689640418454</v>
       </c>
       <c r="G61">
         <v>104.9</v>
@@ -6295,28 +6295,28 @@
         <v>36.717</v>
       </c>
       <c r="M61">
-        <v>21.90100331770331</v>
+        <v>22.27220676376608</v>
       </c>
       <c r="N61">
-        <v>14.81599668229669</v>
+        <v>14.44479323623392</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>14.81599668229669</v>
+        <v>14.44479323623392</v>
       </c>
       <c r="Q61">
-        <v>15.57999668229668</v>
+        <v>15.20879323623392</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09890722879489233</v>
+        <v>0.1002349095147646</v>
       </c>
       <c r="T61">
-        <v>1.035158737645426</v>
+        <v>1.061037706086562</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.676498536042886</v>
+        <v>1.648556893775505</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09409396380590586</v>
+        <v>0.09453596380590586</v>
       </c>
       <c r="C62">
-        <v>96.99680628743141</v>
+        <v>91.98993888165913</v>
       </c>
       <c r="D62">
-        <v>239.5657703292768</v>
+        <v>238.6833856575352</v>
       </c>
       <c r="E62">
-        <v>245.0206906387698</v>
+        <v>249.1451733728005</v>
       </c>
       <c r="F62">
-        <v>247.4689640418454</v>
+        <v>251.5934467758761</v>
       </c>
       <c r="G62">
         <v>104.9</v>
@@ -6377,28 +6377,28 @@
         <v>36.717</v>
       </c>
       <c r="M62">
-        <v>22.27220676376608</v>
+        <v>22.64341020982885</v>
       </c>
       <c r="N62">
-        <v>14.44479323623392</v>
+        <v>14.07358979017115</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>14.44479323623392</v>
+        <v>14.07358979017115</v>
       </c>
       <c r="Q62">
-        <v>15.20879323623392</v>
+        <v>14.83758979017115</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1002349095147646</v>
+        <v>0.1016306764253996</v>
       </c>
       <c r="T62">
-        <v>1.061037706086562</v>
+        <v>1.088243801114422</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.648556893775505</v>
+        <v>1.621531370926726</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09453596380590586</v>
+        <v>0.09497796380590585</v>
       </c>
       <c r="C63">
-        <v>91.98993888165913</v>
+        <v>86.98954773858813</v>
       </c>
       <c r="D63">
-        <v>238.6833856575352</v>
+        <v>237.807477248495</v>
       </c>
       <c r="E63">
-        <v>249.1451733728005</v>
+        <v>253.2696561068313</v>
       </c>
       <c r="F63">
-        <v>251.5934467758761</v>
+        <v>255.7179295099069</v>
       </c>
       <c r="G63">
         <v>104.9</v>
@@ -6459,28 +6459,28 @@
         <v>36.717</v>
       </c>
       <c r="M63">
-        <v>22.64341020982885</v>
+        <v>23.01461365589162</v>
       </c>
       <c r="N63">
-        <v>14.07358979017115</v>
+        <v>13.70238634410838</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>14.07358979017115</v>
+        <v>13.70238634410838</v>
       </c>
       <c r="Q63">
-        <v>14.83758979017115</v>
+        <v>14.46638634410838</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1016306764253996</v>
+        <v>0.1030999047523838</v>
       </c>
       <c r="T63">
-        <v>1.088243801114422</v>
+        <v>1.116881795880592</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.621531370926726</v>
+        <v>1.595377639137585</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09497796380590585</v>
+        <v>0.09541996380590587</v>
       </c>
       <c r="C64">
-        <v>86.98954773858813</v>
+        <v>81.99556182011111</v>
       </c>
       <c r="D64">
-        <v>237.807477248495</v>
+        <v>236.9379740640487</v>
       </c>
       <c r="E64">
-        <v>253.2696561068313</v>
+        <v>257.394138840862</v>
       </c>
       <c r="F64">
-        <v>255.7179295099069</v>
+        <v>259.8424122439376</v>
       </c>
       <c r="G64">
         <v>104.9</v>
@@ -6541,28 +6541,28 @@
         <v>36.717</v>
       </c>
       <c r="M64">
-        <v>23.01461365589162</v>
+        <v>23.38581710195439</v>
       </c>
       <c r="N64">
-        <v>13.70238634410838</v>
+        <v>13.33118289804561</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>13.70238634410838</v>
+        <v>13.33118289804561</v>
       </c>
       <c r="Q64">
-        <v>14.46638634410838</v>
+        <v>14.09518289804561</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1030999047523838</v>
+        <v>0.1046485508267726</v>
       </c>
       <c r="T64">
-        <v>1.116881795880592</v>
+        <v>1.147067790363851</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.595377639137585</v>
+        <v>1.5700541845481</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09541996380590587</v>
+        <v>0.09586196380590585</v>
       </c>
       <c r="C65">
-        <v>81.99556182011111</v>
+        <v>77.00791112329131</v>
       </c>
       <c r="D65">
-        <v>236.9379740640487</v>
+        <v>236.0748061012597</v>
       </c>
       <c r="E65">
-        <v>257.394138840862</v>
+        <v>261.5186215748928</v>
       </c>
       <c r="F65">
-        <v>259.8424122439376</v>
+        <v>263.9668949779684</v>
       </c>
       <c r="G65">
         <v>104.9</v>
@@ -6623,28 +6623,28 @@
         <v>36.717</v>
       </c>
       <c r="M65">
-        <v>23.38581710195439</v>
+        <v>23.75702054801716</v>
       </c>
       <c r="N65">
-        <v>13.33118289804561</v>
+        <v>12.95997945198284</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>13.33118289804561</v>
+        <v>12.95997945198284</v>
       </c>
       <c r="Q65">
-        <v>14.09518289804561</v>
+        <v>13.72397945198284</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1046485508267726</v>
+        <v>0.1062832327941829</v>
       </c>
       <c r="T65">
-        <v>1.147067790363851</v>
+        <v>1.178930784540624</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.5700541845481</v>
+        <v>1.545522087914536</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09586196380590585</v>
+        <v>0.09630396380590586</v>
       </c>
       <c r="C66">
-        <v>77.00791112329131</v>
+        <v>72.02652666157564</v>
       </c>
       <c r="D66">
-        <v>236.0748061012597</v>
+        <v>235.2179043735748</v>
       </c>
       <c r="E66">
-        <v>261.5186215748928</v>
+        <v>265.6431043089235</v>
       </c>
       <c r="F66">
-        <v>263.9668949779684</v>
+        <v>268.0913777119991</v>
       </c>
       <c r="G66">
         <v>104.9</v>
@@ -6705,28 +6705,28 @@
         <v>36.717</v>
       </c>
       <c r="M66">
-        <v>23.75702054801716</v>
+        <v>24.12822399407992</v>
       </c>
       <c r="N66">
-        <v>12.95997945198284</v>
+        <v>12.58877600592008</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>12.95997945198284</v>
+        <v>12.58877600592008</v>
       </c>
       <c r="Q66">
-        <v>13.72397945198284</v>
+        <v>13.35277600592008</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1062832327941829</v>
+        <v>0.108011325159731</v>
       </c>
       <c r="T66">
-        <v>1.178930784540624</v>
+        <v>1.212614521241785</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.545522087914536</v>
+        <v>1.521744825023543</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09630396380590586</v>
+        <v>0.1342339638059059</v>
       </c>
       <c r="C67">
-        <v>72.02652666157564</v>
+        <v>12.03600807419292</v>
       </c>
       <c r="D67">
-        <v>235.2179043735748</v>
+        <v>179.3518685202229</v>
       </c>
       <c r="E67">
-        <v>265.6431043089235</v>
+        <v>269.7675870429543</v>
       </c>
       <c r="F67">
-        <v>268.0913777119991</v>
+        <v>272.2158604460299</v>
       </c>
       <c r="G67">
         <v>104.9</v>
@@ -6787,45 +6787,45 @@
         <v>36.717</v>
       </c>
       <c r="M67">
-        <v>24.12822399407992</v>
+        <v>39.9612883134772</v>
       </c>
       <c r="N67">
-        <v>12.58877600592008</v>
+        <v>-3.244288313477199</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P67">
-        <v>12.58877600592008</v>
+        <v>-3.244288313477199</v>
       </c>
       <c r="Q67">
-        <v>13.35277600592008</v>
+        <v>-2.480288313477199</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.108011325159731</v>
+        <v>0.1098410700173702</v>
       </c>
       <c r="T67">
-        <v>1.212614521241785</v>
+        <v>1.248279654219485</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.521744825023543</v>
+        <v>0.9188142212025971</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1342339638059059</v>
+        <v>0.1352439638059059</v>
       </c>
       <c r="C68">
-        <v>12.03600807419292</v>
+        <v>6.784369582300997</v>
       </c>
       <c r="D68">
-        <v>179.3518685202229</v>
+        <v>178.2247127623617</v>
       </c>
       <c r="E68">
-        <v>269.7675870429543</v>
+        <v>273.8920697769851</v>
       </c>
       <c r="F68">
-        <v>272.2158604460299</v>
+        <v>276.3403431800607</v>
       </c>
       <c r="G68">
         <v>104.9</v>
@@ -6869,28 +6869,28 @@
         <v>36.717</v>
       </c>
       <c r="M68">
-        <v>39.9612883134772</v>
+        <v>40.56676237883291</v>
       </c>
       <c r="N68">
-        <v>-3.244288313477199</v>
+        <v>-3.849762378832914</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-3.244288313477199</v>
+        <v>-3.849762378832914</v>
       </c>
       <c r="Q68">
-        <v>-2.480288313477199</v>
+        <v>-3.085762378832913</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1098410700173702</v>
+        <v>0.111781708502745</v>
       </c>
       <c r="T68">
-        <v>1.248279654219485</v>
+        <v>1.286106310407954</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9188142212025971</v>
+        <v>0.905100576110021</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1352439638059059</v>
+        <v>0.1362539638059059</v>
       </c>
       <c r="C69">
-        <v>6.784369582300997</v>
+        <v>1.546810068368472</v>
       </c>
       <c r="D69">
-        <v>178.2247127623617</v>
+        <v>177.1116359824599</v>
       </c>
       <c r="E69">
-        <v>273.8920697769851</v>
+        <v>278.0165525110158</v>
       </c>
       <c r="F69">
-        <v>276.3403431800607</v>
+        <v>280.4648259140915</v>
       </c>
       <c r="G69">
         <v>104.9</v>
@@ -6951,28 +6951,28 @@
         <v>36.717</v>
       </c>
       <c r="M69">
-        <v>40.56676237883291</v>
+        <v>41.17223644418863</v>
       </c>
       <c r="N69">
-        <v>-3.849762378832914</v>
+        <v>-4.455236444188635</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-3.849762378832914</v>
+        <v>-4.455236444188635</v>
       </c>
       <c r="Q69">
-        <v>-3.085762378832913</v>
+        <v>-3.691236444188635</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.111781708502745</v>
+        <v>0.1138436368934558</v>
       </c>
       <c r="T69">
-        <v>1.286106310407954</v>
+        <v>1.326297132608203</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.905100576110021</v>
+        <v>0.8917902735201677</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1362539638059059</v>
+        <v>0.1372639638059059</v>
       </c>
       <c r="C70">
-        <v>1.546810068368472</v>
+        <v>-3.676932615088788</v>
       </c>
       <c r="D70">
-        <v>177.1116359824599</v>
+        <v>176.0123760330334</v>
       </c>
       <c r="E70">
-        <v>278.0165525110158</v>
+        <v>282.1410352450466</v>
       </c>
       <c r="F70">
-        <v>280.4648259140915</v>
+        <v>284.5893086481222</v>
       </c>
       <c r="G70">
         <v>104.9</v>
@@ -7033,28 +7033,28 @@
         <v>36.717</v>
       </c>
       <c r="M70">
-        <v>41.17223644418863</v>
+        <v>41.77771050954434</v>
       </c>
       <c r="N70">
-        <v>-4.455236444188635</v>
+        <v>-5.060710509544343</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-4.455236444188635</v>
+        <v>-5.060710509544343</v>
       </c>
       <c r="Q70">
-        <v>-3.691236444188635</v>
+        <v>-4.296710509544343</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1138436368934558</v>
+        <v>0.116038592922277</v>
       </c>
       <c r="T70">
-        <v>1.326297132608203</v>
+        <v>1.369080911079435</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8917902735201677</v>
+        <v>0.8788657768024842</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1372639638059059</v>
+        <v>0.1382739638059059</v>
       </c>
       <c r="C71">
-        <v>-3.676932615088788</v>
+        <v>-8.887114147527768</v>
       </c>
       <c r="D71">
-        <v>176.0123760330334</v>
+        <v>174.9266772346252</v>
       </c>
       <c r="E71">
-        <v>282.1410352450466</v>
+        <v>286.2655179790773</v>
       </c>
       <c r="F71">
-        <v>284.5893086481222</v>
+        <v>288.713791382153</v>
       </c>
       <c r="G71">
         <v>104.9</v>
@@ -7115,28 +7115,28 @@
         <v>36.717</v>
       </c>
       <c r="M71">
-        <v>41.77771050954434</v>
+        <v>42.38318457490006</v>
       </c>
       <c r="N71">
-        <v>-5.060710509544343</v>
+        <v>-5.666184574900065</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-5.060710509544343</v>
+        <v>-5.666184574900065</v>
       </c>
       <c r="Q71">
-        <v>-4.296710509544343</v>
+        <v>-4.902184574900065</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.116038592922277</v>
+        <v>0.1183798793530196</v>
       </c>
       <c r="T71">
-        <v>1.369080911079435</v>
+        <v>1.414716941448749</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8788657768024842</v>
+        <v>0.8663105514195915</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1382739638059059</v>
+        <v>0.1392839638059059</v>
       </c>
       <c r="C72">
-        <v>-8.887114147527768</v>
+        <v>-14.08398393863939</v>
       </c>
       <c r="D72">
-        <v>174.9266772346252</v>
+        <v>173.8542901775443</v>
       </c>
       <c r="E72">
-        <v>286.2655179790773</v>
+        <v>290.3900007131081</v>
       </c>
       <c r="F72">
-        <v>288.713791382153</v>
+        <v>292.8382741161838</v>
       </c>
       <c r="G72">
         <v>104.9</v>
@@ -7197,28 +7197,28 @@
         <v>36.717</v>
       </c>
       <c r="M72">
-        <v>42.38318457490006</v>
+        <v>42.98865864025578</v>
       </c>
       <c r="N72">
-        <v>-5.666184574900065</v>
+        <v>-6.271658640255779</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-5.666184574900065</v>
+        <v>-6.271658640255779</v>
       </c>
       <c r="Q72">
-        <v>-4.902184574900065</v>
+        <v>-5.507658640255779</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1183798793530196</v>
+        <v>0.1208826338134685</v>
       </c>
       <c r="T72">
-        <v>1.414716941448749</v>
+        <v>1.463500284257327</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8663105514195915</v>
+        <v>0.8541089943573438</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1392839638059059</v>
+        <v>0.1402939638059059</v>
       </c>
       <c r="C73">
-        <v>-14.08398393863934</v>
+        <v>-19.26778531936117</v>
       </c>
       <c r="D73">
-        <v>173.8542901775444</v>
+        <v>172.7949715308532</v>
       </c>
       <c r="E73">
-        <v>290.3900007131081</v>
+        <v>294.5144834471388</v>
       </c>
       <c r="F73">
-        <v>292.8382741161837</v>
+        <v>296.9627568502144</v>
       </c>
       <c r="G73">
         <v>104.9</v>
@@ -7279,28 +7279,28 @@
         <v>36.717</v>
       </c>
       <c r="M73">
-        <v>42.98865864025577</v>
+        <v>43.59413270561148</v>
       </c>
       <c r="N73">
-        <v>-6.271658640255772</v>
+        <v>-6.87713270561148</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-6.271658640255772</v>
+        <v>-6.87713270561148</v>
       </c>
       <c r="Q73">
-        <v>-5.507658640255772</v>
+        <v>-6.11313270561148</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1208826338134685</v>
+        <v>0.1235641564496638</v>
       </c>
       <c r="T73">
-        <v>1.463500284257327</v>
+        <v>1.515768151552231</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8541089943573439</v>
+        <v>0.8422463694357143</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1402939638059059</v>
+        <v>0.1413039638059059</v>
       </c>
       <c r="C74">
-        <v>-19.26778531936117</v>
+        <v>-24.43875572594931</v>
       </c>
       <c r="D74">
-        <v>172.7949715308532</v>
+        <v>171.7484838582959</v>
       </c>
       <c r="E74">
-        <v>294.5144834471388</v>
+        <v>298.6389661811696</v>
       </c>
       <c r="F74">
-        <v>296.9627568502144</v>
+        <v>301.0872395842452</v>
       </c>
       <c r="G74">
         <v>104.9</v>
@@ -7361,28 +7361,28 @@
         <v>36.717</v>
       </c>
       <c r="M74">
-        <v>43.59413270561148</v>
+        <v>44.1996067709672</v>
       </c>
       <c r="N74">
-        <v>-6.87713270561148</v>
+        <v>-7.482606770967202</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-6.87713270561148</v>
+        <v>-7.482606770967202</v>
       </c>
       <c r="Q74">
-        <v>-6.11313270561148</v>
+        <v>-6.718606770967201</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1235641564496638</v>
+        <v>0.1264443103922439</v>
       </c>
       <c r="T74">
-        <v>1.515768151552231</v>
+        <v>1.571907712720832</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8422463694357143</v>
+        <v>0.8307087479365948</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1413039638059059</v>
+        <v>0.1423139638059059</v>
       </c>
       <c r="C75">
-        <v>-24.43875572594931</v>
+        <v>-29.59712687740193</v>
       </c>
       <c r="D75">
-        <v>171.7484838582959</v>
+        <v>170.714595440874</v>
       </c>
       <c r="E75">
-        <v>298.6389661811696</v>
+        <v>302.7634489152003</v>
       </c>
       <c r="F75">
-        <v>301.0872395842452</v>
+        <v>305.211722318276</v>
       </c>
       <c r="G75">
         <v>104.9</v>
@@ -7443,28 +7443,28 @@
         <v>36.717</v>
       </c>
       <c r="M75">
-        <v>44.1996067709672</v>
+        <v>44.80508083632292</v>
       </c>
       <c r="N75">
-        <v>-7.482606770967202</v>
+        <v>-8.088080836322916</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-7.482606770967202</v>
+        <v>-8.088080836322916</v>
       </c>
       <c r="Q75">
-        <v>-6.718606770967201</v>
+        <v>-7.324080836322916</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1264443103922439</v>
+        <v>0.1295460146380994</v>
       </c>
       <c r="T75">
-        <v>1.571907712720832</v>
+        <v>1.632365701671634</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8307087479365948</v>
+        <v>0.8194829540455597</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1423139638059059</v>
+        <v>0.1433239638059059</v>
       </c>
       <c r="C76">
-        <v>-29.59712687740193</v>
+        <v>-34.74312494651281</v>
       </c>
       <c r="D76">
-        <v>170.714595440874</v>
+        <v>169.6930801057939</v>
       </c>
       <c r="E76">
-        <v>302.7634489152003</v>
+        <v>306.8879316492311</v>
       </c>
       <c r="F76">
-        <v>305.211722318276</v>
+        <v>309.3362050523067</v>
       </c>
       <c r="G76">
         <v>104.9</v>
@@ -7525,28 +7525,28 @@
         <v>36.717</v>
       </c>
       <c r="M76">
-        <v>44.80508083632292</v>
+        <v>45.41055490167863</v>
       </c>
       <c r="N76">
-        <v>-8.088080836322916</v>
+        <v>-8.693554901678631</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-8.088080836322916</v>
+        <v>-8.693554901678631</v>
       </c>
       <c r="Q76">
-        <v>-7.324080836322916</v>
+        <v>-7.929554901678631</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1295460146380994</v>
+        <v>0.1328958552236234</v>
       </c>
       <c r="T76">
-        <v>1.632365701671634</v>
+        <v>1.697660329738499</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8194829540455597</v>
+        <v>0.8085565146582856</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1433239638059059</v>
+        <v>0.1853739638059058</v>
       </c>
       <c r="C77">
-        <v>-34.74312494651281</v>
+        <v>-72.7112258407698</v>
       </c>
       <c r="D77">
-        <v>169.6930801057939</v>
+        <v>135.8494619455677</v>
       </c>
       <c r="E77">
-        <v>306.8879316492311</v>
+        <v>311.0124143832618</v>
       </c>
       <c r="F77">
-        <v>309.3362050523067</v>
+        <v>313.4606877863375</v>
       </c>
       <c r="G77">
         <v>104.9</v>
@@ -7607,45 +7607,45 @@
         <v>36.717</v>
       </c>
       <c r="M77">
-        <v>45.41055490167863</v>
+        <v>62.94290610749657</v>
       </c>
       <c r="N77">
-        <v>-8.693554901678631</v>
+        <v>-26.22590610749657</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-8.693554901678631</v>
+        <v>-26.22590610749657</v>
       </c>
       <c r="Q77">
-        <v>-7.929554901678631</v>
+        <v>-25.46190610749657</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1328958552236234</v>
+        <v>0.1365248491912744</v>
       </c>
       <c r="T77">
-        <v>1.697660329738499</v>
+        <v>1.768396176810937</v>
       </c>
       <c r="U77">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8085565146582856</v>
+        <v>0.5833381753504223</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1853739638059058</v>
+        <v>0.1869239638059059</v>
       </c>
       <c r="C78">
-        <v>-72.7112258407698</v>
+        <v>-77.82712296803288</v>
       </c>
       <c r="D78">
-        <v>135.8494619455677</v>
+        <v>134.8580475523354</v>
       </c>
       <c r="E78">
-        <v>311.0124143832618</v>
+        <v>315.1368971172926</v>
       </c>
       <c r="F78">
-        <v>313.4606877863375</v>
+        <v>317.5851705203683</v>
       </c>
       <c r="G78">
         <v>104.9</v>
@@ -7689,28 +7689,28 @@
         <v>36.717</v>
       </c>
       <c r="M78">
-        <v>62.94290610749657</v>
+        <v>63.77110224048995</v>
       </c>
       <c r="N78">
-        <v>-26.22590610749657</v>
+        <v>-27.05410224048995</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-26.22590610749657</v>
+        <v>-27.05410224048995</v>
       </c>
       <c r="Q78">
-        <v>-25.46190610749657</v>
+        <v>-26.29010224048995</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1365248491912744</v>
+        <v>0.1404694078517646</v>
       </c>
       <c r="T78">
-        <v>1.768396176810937</v>
+        <v>1.845282967107064</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5833381753504223</v>
+        <v>0.5757623548913259</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1869239638059059</v>
+        <v>0.1884739638059059</v>
       </c>
       <c r="C79">
-        <v>-77.82712296803288</v>
+        <v>-82.92865446822006</v>
       </c>
       <c r="D79">
-        <v>134.8580475523354</v>
+        <v>133.880998786179</v>
       </c>
       <c r="E79">
-        <v>315.1368971172926</v>
+        <v>319.2613798513234</v>
       </c>
       <c r="F79">
-        <v>317.5851705203683</v>
+        <v>321.709653254399</v>
       </c>
       <c r="G79">
         <v>104.9</v>
@@ -7771,28 +7771,28 @@
         <v>36.717</v>
       </c>
       <c r="M79">
-        <v>63.77110224048995</v>
+        <v>64.59929837348332</v>
       </c>
       <c r="N79">
-        <v>-27.05410224048995</v>
+        <v>-27.88229837348332</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-27.05410224048995</v>
+        <v>-27.88229837348332</v>
       </c>
       <c r="Q79">
-        <v>-26.29010224048995</v>
+        <v>-27.11829837348332</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1404694078517646</v>
+        <v>0.1447725627541175</v>
       </c>
       <c r="T79">
-        <v>1.845282967107064</v>
+        <v>1.929159465611931</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5757623548913259</v>
+        <v>0.568380786238873</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1884739638059059</v>
+        <v>0.1900239638059059</v>
       </c>
       <c r="C80">
-        <v>-82.92865446822006</v>
+        <v>-88.01613033304758</v>
       </c>
       <c r="D80">
-        <v>133.880998786179</v>
+        <v>132.9180056553822</v>
       </c>
       <c r="E80">
-        <v>319.2613798513234</v>
+        <v>323.3858625853541</v>
       </c>
       <c r="F80">
-        <v>321.709653254399</v>
+        <v>325.8341359884298</v>
       </c>
       <c r="G80">
         <v>104.9</v>
@@ -7853,28 +7853,28 @@
         <v>36.717</v>
       </c>
       <c r="M80">
-        <v>64.59929837348332</v>
+        <v>65.42749450647669</v>
       </c>
       <c r="N80">
-        <v>-27.88229837348332</v>
+        <v>-28.71049450647669</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-27.88229837348332</v>
+        <v>-28.71049450647669</v>
       </c>
       <c r="Q80">
-        <v>-27.11829837348332</v>
+        <v>-27.94649450647669</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1447725627541175</v>
+        <v>0.149485541932885</v>
       </c>
       <c r="T80">
-        <v>1.929159465611931</v>
+        <v>2.021024202069642</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.568380786238873</v>
+        <v>0.5611860927421785</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1900239638059059</v>
+        <v>0.1915739638059059</v>
       </c>
       <c r="C81">
-        <v>-88.01613033304758</v>
+        <v>-93.08985169896451</v>
       </c>
       <c r="D81">
-        <v>132.9180056553822</v>
+        <v>131.968767023496</v>
       </c>
       <c r="E81">
-        <v>323.3858625853541</v>
+        <v>327.5103453193849</v>
       </c>
       <c r="F81">
-        <v>325.8341359884298</v>
+        <v>329.9586187224605</v>
       </c>
       <c r="G81">
         <v>104.9</v>
@@ -7935,28 +7935,28 @@
         <v>36.717</v>
       </c>
       <c r="M81">
-        <v>65.42749450647669</v>
+        <v>66.25569063947007</v>
       </c>
       <c r="N81">
-        <v>-28.71049450647669</v>
+        <v>-29.53869063947008</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-28.71049450647669</v>
+        <v>-29.53869063947008</v>
       </c>
       <c r="Q81">
-        <v>-27.94649450647669</v>
+        <v>-28.77469063947008</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.149485541932885</v>
+        <v>0.1546698190295293</v>
       </c>
       <c r="T81">
-        <v>2.021024202069642</v>
+        <v>2.122075412173124</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5611860927421785</v>
+        <v>0.5541712665829012</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1915739638059059</v>
+        <v>0.1931239638059059</v>
       </c>
       <c r="C82">
-        <v>-93.08985169896451</v>
+        <v>-98.1501111611116</v>
       </c>
       <c r="D82">
-        <v>131.968767023496</v>
+        <v>131.0329902953797</v>
       </c>
       <c r="E82">
-        <v>327.5103453193849</v>
+        <v>331.6348280534157</v>
       </c>
       <c r="F82">
-        <v>329.9586187224605</v>
+        <v>334.0831014564913</v>
       </c>
       <c r="G82">
         <v>104.9</v>
@@ -8017,28 +8017,28 @@
         <v>36.717</v>
       </c>
       <c r="M82">
-        <v>66.25569063947007</v>
+        <v>67.08388677246346</v>
       </c>
       <c r="N82">
-        <v>-29.53869063947008</v>
+        <v>-30.36688677246346</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-29.53869063947008</v>
+        <v>-30.36688677246346</v>
       </c>
       <c r="Q82">
-        <v>-28.77469063947008</v>
+        <v>-29.60288677246346</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1546698190295293</v>
+        <v>0.1603998095047677</v>
       </c>
       <c r="T82">
-        <v>2.122075412173124</v>
+        <v>2.233763591761184</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5541712665829012</v>
+        <v>0.5473296460078035</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1931239638059059</v>
+        <v>0.1946739638059059</v>
       </c>
       <c r="C83">
-        <v>-98.1501111611116</v>
+        <v>-103.1971930740166</v>
       </c>
       <c r="D83">
-        <v>131.0329902953797</v>
+        <v>130.1103911165054</v>
       </c>
       <c r="E83">
-        <v>331.6348280534157</v>
+        <v>335.7593107874464</v>
       </c>
       <c r="F83">
-        <v>334.0831014564913</v>
+        <v>338.207584190522</v>
       </c>
       <c r="G83">
         <v>104.9</v>
@@ -8099,28 +8099,28 @@
         <v>36.717</v>
       </c>
       <c r="M83">
-        <v>67.08388677246346</v>
+        <v>67.91208290545683</v>
       </c>
       <c r="N83">
-        <v>-30.36688677246346</v>
+        <v>-31.19508290545683</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-30.36688677246346</v>
+        <v>-31.19508290545683</v>
       </c>
       <c r="Q83">
-        <v>-29.60288677246346</v>
+        <v>-30.43108290545683</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1603998095047677</v>
+        <v>0.1667664655883659</v>
       </c>
       <c r="T83">
-        <v>2.233763591761184</v>
+        <v>2.357861569081249</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5473296460078035</v>
+        <v>0.5406548942272207</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1946739638059059</v>
+        <v>0.1962239638059059</v>
       </c>
       <c r="C84">
-        <v>-103.1971930740166</v>
+        <v>-108.2313738396759</v>
       </c>
       <c r="D84">
-        <v>130.1103911165054</v>
+        <v>129.2006930848769</v>
       </c>
       <c r="E84">
-        <v>335.7593107874464</v>
+        <v>339.8837935214772</v>
       </c>
       <c r="F84">
-        <v>338.207584190522</v>
+        <v>342.3320669245528</v>
       </c>
       <c r="G84">
         <v>104.9</v>
@@ -8181,28 +8181,28 @@
         <v>36.717</v>
       </c>
       <c r="M84">
-        <v>67.91208290545683</v>
+        <v>68.74027903845021</v>
       </c>
       <c r="N84">
-        <v>-31.19508290545683</v>
+        <v>-32.02327903845021</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-31.19508290545683</v>
+        <v>-32.02327903845021</v>
       </c>
       <c r="Q84">
-        <v>-30.43108290545683</v>
+        <v>-31.25927903845021</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1667664655883659</v>
+        <v>0.1738821400347404</v>
       </c>
       <c r="T84">
-        <v>2.357861569081249</v>
+        <v>2.49655930843897</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5406548942272207</v>
+        <v>0.5341409798389408</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1962239638059059</v>
+        <v>0.1977739638059059</v>
       </c>
       <c r="C85">
-        <v>-108.2313738396759</v>
+        <v>-113.2529221836336</v>
       </c>
       <c r="D85">
-        <v>129.2006930848769</v>
+        <v>128.3036274749499</v>
       </c>
       <c r="E85">
-        <v>339.8837935214772</v>
+        <v>344.008276255508</v>
       </c>
       <c r="F85">
-        <v>342.3320669245528</v>
+        <v>346.4565496585836</v>
       </c>
       <c r="G85">
         <v>104.9</v>
@@ -8263,28 +8263,28 @@
         <v>36.717</v>
       </c>
       <c r="M85">
-        <v>68.74027903845021</v>
+        <v>69.56847517144358</v>
       </c>
       <c r="N85">
-        <v>-32.02327903845021</v>
+        <v>-32.85147517144358</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-32.02327903845021</v>
+        <v>-32.85147517144358</v>
       </c>
       <c r="Q85">
-        <v>-31.25927903845021</v>
+        <v>-32.08747517144358</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1738821400347404</v>
+        <v>0.1818872737869117</v>
       </c>
       <c r="T85">
-        <v>2.49655930843897</v>
+        <v>2.652594265216406</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5341409798389408</v>
+        <v>0.527782158650382</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1977739638059058</v>
+        <v>0.1993239638059059</v>
       </c>
       <c r="C86">
-        <v>-113.2529221836336</v>
+        <v>-118.26209941964</v>
       </c>
       <c r="D86">
-        <v>128.30362747495</v>
+        <v>127.4189329729743</v>
       </c>
       <c r="E86">
-        <v>344.0082762555079</v>
+        <v>348.1327589895387</v>
       </c>
       <c r="F86">
-        <v>346.4565496585835</v>
+        <v>350.5810323926143</v>
       </c>
       <c r="G86">
         <v>104.9</v>
@@ -8345,28 +8345,28 @@
         <v>36.717</v>
       </c>
       <c r="M86">
-        <v>69.56847517144358</v>
+        <v>70.39667130443695</v>
       </c>
       <c r="N86">
-        <v>-32.85147517144358</v>
+        <v>-33.67967130443695</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-32.85147517144358</v>
+        <v>-33.67967130443695</v>
       </c>
       <c r="Q86">
-        <v>-32.08747517144358</v>
+        <v>-32.91567130443695</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1818872737869116</v>
+        <v>0.190959758706039</v>
       </c>
       <c r="T86">
-        <v>2.652594265216405</v>
+        <v>2.829433882897498</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.527782158650382</v>
+        <v>0.5215729567839069</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1993239638059059</v>
+        <v>0.2008739638059059</v>
       </c>
       <c r="C87">
-        <v>-118.26209941964</v>
+        <v>-123.2591597034352</v>
       </c>
       <c r="D87">
-        <v>127.4189329729743</v>
+        <v>126.5463554232099</v>
       </c>
       <c r="E87">
-        <v>348.1327589895387</v>
+        <v>352.2572417235694</v>
       </c>
       <c r="F87">
-        <v>350.5810323926143</v>
+        <v>354.705515126645</v>
       </c>
       <c r="G87">
         <v>104.9</v>
@@ -8427,28 +8427,28 @@
         <v>36.717</v>
       </c>
       <c r="M87">
-        <v>70.39667130443695</v>
+        <v>71.22486743743032</v>
       </c>
       <c r="N87">
-        <v>-33.67967130443695</v>
+        <v>-34.50786743743032</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-33.67967130443695</v>
+        <v>-34.50786743743032</v>
       </c>
       <c r="Q87">
-        <v>-32.91567130443695</v>
+        <v>-33.74386743743032</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.190959758706039</v>
+        <v>0.2013283128993276</v>
       </c>
       <c r="T87">
-        <v>2.829433882897498</v>
+        <v>3.031536303104462</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5215729567839069</v>
+        <v>0.5155081549608383</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2008739638059059</v>
+        <v>0.2024239638059059</v>
       </c>
       <c r="C88">
-        <v>-123.2591597034352</v>
+        <v>-128.2443502761754</v>
       </c>
       <c r="D88">
-        <v>126.5463554232099</v>
+        <v>125.6856475845004</v>
       </c>
       <c r="E88">
-        <v>352.2572417235694</v>
+        <v>356.3817244576002</v>
       </c>
       <c r="F88">
-        <v>354.705515126645</v>
+        <v>358.8299978606758</v>
       </c>
       <c r="G88">
         <v>104.9</v>
@@ -8509,28 +8509,28 @@
         <v>36.717</v>
       </c>
       <c r="M88">
-        <v>71.22486743743032</v>
+        <v>72.0530635704237</v>
       </c>
       <c r="N88">
-        <v>-34.50786743743032</v>
+        <v>-35.3360635704237</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-34.50786743743032</v>
+        <v>-35.3360635704237</v>
       </c>
       <c r="Q88">
-        <v>-33.74386743743032</v>
+        <v>-34.5720635704237</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2013283128993276</v>
+        <v>0.2132920292761989</v>
       </c>
       <c r="T88">
-        <v>3.031536303104462</v>
+        <v>3.264731403343267</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5155081549608383</v>
+        <v>0.5095827738693344</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2024239638059059</v>
+        <v>0.2039739638059059</v>
       </c>
       <c r="C89">
-        <v>-128.2443502761754</v>
+        <v>-133.2179116979934</v>
       </c>
       <c r="D89">
-        <v>125.6856475845004</v>
+        <v>124.8365688967132</v>
       </c>
       <c r="E89">
-        <v>356.3817244576002</v>
+        <v>360.5062071916309</v>
       </c>
       <c r="F89">
-        <v>358.8299978606758</v>
+        <v>362.9544805947066</v>
       </c>
       <c r="G89">
         <v>104.9</v>
@@ -8591,28 +8591,28 @@
         <v>36.717</v>
       </c>
       <c r="M89">
-        <v>72.0530635704237</v>
+        <v>72.88125970341709</v>
       </c>
       <c r="N89">
-        <v>-35.3360635704237</v>
+        <v>-36.16425970341709</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-35.3360635704237</v>
+        <v>-36.16425970341709</v>
       </c>
       <c r="Q89">
-        <v>-34.5720635704237</v>
+        <v>-35.40025970341708</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2132920292761989</v>
+        <v>0.2272496983825488</v>
       </c>
       <c r="T89">
-        <v>3.264731403343267</v>
+        <v>3.536792353621873</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5095827738693344</v>
+        <v>0.5037920605299101</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2039739638059059</v>
+        <v>0.2366739638059059</v>
       </c>
       <c r="C90">
-        <v>-133.2179116979934</v>
+        <v>-152.9148108585726</v>
       </c>
       <c r="D90">
-        <v>124.8365688967132</v>
+        <v>109.2641524701647</v>
       </c>
       <c r="E90">
-        <v>360.5062071916309</v>
+        <v>364.6306899256617</v>
       </c>
       <c r="F90">
-        <v>362.9544805947066</v>
+        <v>367.0789633287373</v>
       </c>
       <c r="G90">
         <v>104.9</v>
@@ -8673,45 +8673,45 @@
         <v>36.717</v>
       </c>
       <c r="M90">
-        <v>72.88125970341709</v>
+        <v>86.55721955291627</v>
       </c>
       <c r="N90">
-        <v>-36.16425970341709</v>
+        <v>-49.84021955291627</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-36.16425970341709</v>
+        <v>-49.84021955291627</v>
       </c>
       <c r="Q90">
-        <v>-35.40025970341708</v>
+        <v>-49.07621955291626</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2272496983825488</v>
+        <v>0.2437451255082351</v>
       </c>
       <c r="T90">
-        <v>3.536792353621873</v>
+        <v>3.858318931223862</v>
       </c>
       <c r="U90">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.5037920605299101</v>
+        <v>0.4241933854813031</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2366739638059059</v>
+        <v>0.2385739638059059</v>
       </c>
       <c r="C91">
-        <v>-152.9148108585726</v>
+        <v>-157.8255447681644</v>
       </c>
       <c r="D91">
-        <v>109.2641524701647</v>
+        <v>108.4779012946036</v>
       </c>
       <c r="E91">
-        <v>364.6306899256617</v>
+        <v>368.7551726596924</v>
       </c>
       <c r="F91">
-        <v>367.0789633287373</v>
+        <v>371.2034460627681</v>
       </c>
       <c r="G91">
         <v>104.9</v>
@@ -8755,28 +8755,28 @@
         <v>36.717</v>
       </c>
       <c r="M91">
-        <v>86.55721955291627</v>
+        <v>87.52977258160071</v>
       </c>
       <c r="N91">
-        <v>-49.84021955291627</v>
+        <v>-50.81277258160071</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-49.84021955291627</v>
+        <v>-50.81277258160071</v>
       </c>
       <c r="Q91">
-        <v>-49.07621955291626</v>
+        <v>-50.04877258160071</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2437451255082351</v>
+        <v>0.2635396380590586</v>
       </c>
       <c r="T91">
-        <v>3.858318931223862</v>
+        <v>4.244150824346248</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4241933854813031</v>
+        <v>0.419480125642622</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2385739638059059</v>
+        <v>0.2404739638059059</v>
       </c>
       <c r="C92">
-        <v>-157.8255447681644</v>
+        <v>-162.7250439909112</v>
       </c>
       <c r="D92">
-        <v>108.4779012946036</v>
+        <v>107.7028848058876</v>
       </c>
       <c r="E92">
-        <v>368.7551726596924</v>
+        <v>372.8796553937232</v>
       </c>
       <c r="F92">
-        <v>371.2034460627681</v>
+        <v>375.3279287967989</v>
       </c>
       <c r="G92">
         <v>104.9</v>
@@ -8837,28 +8837,28 @@
         <v>36.717</v>
       </c>
       <c r="M92">
-        <v>87.52977258160071</v>
+        <v>88.50232561028517</v>
       </c>
       <c r="N92">
-        <v>-50.81277258160071</v>
+        <v>-51.78532561028517</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-50.81277258160071</v>
+        <v>-51.78532561028517</v>
       </c>
       <c r="Q92">
-        <v>-50.04877258160071</v>
+        <v>-51.02132561028517</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2635396380590586</v>
+        <v>0.2877329311767318</v>
       </c>
       <c r="T92">
-        <v>4.244150824346248</v>
+        <v>4.715723138162499</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.419480125642622</v>
+        <v>0.4148704539322635</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2404739638059059</v>
+        <v>0.2423739638059059</v>
       </c>
       <c r="C93">
-        <v>-162.7250439909112</v>
+        <v>-167.6135476161037</v>
       </c>
       <c r="D93">
-        <v>107.7028848058876</v>
+        <v>106.9388639147258</v>
       </c>
       <c r="E93">
-        <v>372.8796553937232</v>
+        <v>377.0041381277539</v>
       </c>
       <c r="F93">
-        <v>375.3279287967989</v>
+        <v>379.4524115308296</v>
       </c>
       <c r="G93">
         <v>104.9</v>
@@ -8919,28 +8919,28 @@
         <v>36.717</v>
       </c>
       <c r="M93">
-        <v>88.50232561028517</v>
+        <v>89.47487863896961</v>
       </c>
       <c r="N93">
-        <v>-51.78532561028517</v>
+        <v>-52.75787863896961</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-51.78532561028517</v>
+        <v>-52.75787863896961</v>
       </c>
       <c r="Q93">
-        <v>-51.02132561028517</v>
+        <v>-51.99387863896961</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2877329311767318</v>
+        <v>0.3179745475738234</v>
       </c>
       <c r="T93">
-        <v>4.715723138162499</v>
+        <v>5.305188530432813</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4148704539322635</v>
+        <v>0.4103609924764781</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2423739638059059</v>
+        <v>0.2442739638059059</v>
       </c>
       <c r="C94">
-        <v>-167.6135476161037</v>
+        <v>-172.4912879966296</v>
       </c>
       <c r="D94">
-        <v>106.9388639147258</v>
+        <v>106.1856062682308</v>
       </c>
       <c r="E94">
-        <v>377.0041381277539</v>
+        <v>381.1286208617847</v>
       </c>
       <c r="F94">
-        <v>379.4524115308296</v>
+        <v>383.5768942648604</v>
       </c>
       <c r="G94">
         <v>104.9</v>
@@ -9001,28 +9001,28 @@
         <v>36.717</v>
       </c>
       <c r="M94">
-        <v>89.47487863896961</v>
+        <v>90.44743166765407</v>
       </c>
       <c r="N94">
-        <v>-52.75787863896961</v>
+        <v>-53.73043166765407</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-52.75787863896961</v>
+        <v>-53.73043166765407</v>
       </c>
       <c r="Q94">
-        <v>-51.99387863896961</v>
+        <v>-52.96643166765407</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3179745475738234</v>
+        <v>0.3568566257986553</v>
       </c>
       <c r="T94">
-        <v>5.305188530432813</v>
+        <v>6.063072606208929</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4103609924764781</v>
+        <v>0.4059485086864084</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2442739638059059</v>
+        <v>0.2461739638059059</v>
       </c>
       <c r="C95">
-        <v>-172.4912879966296</v>
+        <v>-177.3584909845629</v>
       </c>
       <c r="D95">
-        <v>106.1856062682308</v>
+        <v>105.4428860143282</v>
       </c>
       <c r="E95">
-        <v>381.1286208617847</v>
+        <v>385.2531035958155</v>
       </c>
       <c r="F95">
-        <v>383.5768942648604</v>
+        <v>387.7013769988911</v>
       </c>
       <c r="G95">
         <v>104.9</v>
@@ -9083,28 +9083,28 @@
         <v>36.717</v>
       </c>
       <c r="M95">
-        <v>90.44743166765407</v>
+        <v>91.41998469633853</v>
       </c>
       <c r="N95">
-        <v>-53.73043166765407</v>
+        <v>-54.70298469633853</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-53.73043166765407</v>
+        <v>-54.70298469633853</v>
       </c>
       <c r="Q95">
-        <v>-52.96643166765407</v>
+        <v>-53.93898469633853</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3568566257986553</v>
+        <v>0.408699396765098</v>
       </c>
       <c r="T95">
-        <v>6.063072606208929</v>
+        <v>7.073584707243753</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4059485086864084</v>
+        <v>0.40162990753017</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2461739638059059</v>
+        <v>0.2480739638059059</v>
       </c>
       <c r="C96">
-        <v>-177.3584909845629</v>
+        <v>-182.215376156937</v>
       </c>
       <c r="D96">
-        <v>105.4428860143282</v>
+        <v>104.7104835759849</v>
       </c>
       <c r="E96">
-        <v>385.2531035958155</v>
+        <v>389.3775863298462</v>
       </c>
       <c r="F96">
-        <v>387.7013769988911</v>
+        <v>391.8258597329219</v>
       </c>
       <c r="G96">
         <v>104.9</v>
@@ -9165,28 +9165,28 @@
         <v>36.717</v>
       </c>
       <c r="M96">
-        <v>91.41998469633853</v>
+        <v>92.39253772502298</v>
       </c>
       <c r="N96">
-        <v>-54.70298469633853</v>
+        <v>-55.67553772502298</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-54.70298469633853</v>
+        <v>-55.67553772502298</v>
       </c>
       <c r="Q96">
-        <v>-53.93898469633853</v>
+        <v>-54.91153772502297</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.408699396765098</v>
+        <v>0.4812792761181178</v>
       </c>
       <c r="T96">
-        <v>7.073584707243753</v>
+        <v>8.488301648692508</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.40162990753017</v>
+        <v>0.3974022242930103</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2480739638059059</v>
+        <v>0.2499739638059059</v>
       </c>
       <c r="C97">
-        <v>-182.215376156937</v>
+        <v>-187.0621570321717</v>
       </c>
       <c r="D97">
-        <v>104.7104835759849</v>
+        <v>103.9881854347809</v>
       </c>
       <c r="E97">
-        <v>389.3775863298462</v>
+        <v>393.502069063877</v>
       </c>
       <c r="F97">
-        <v>391.8258597329219</v>
+        <v>395.9503424669526</v>
       </c>
       <c r="G97">
         <v>104.9</v>
@@ -9247,28 +9247,28 @@
         <v>36.717</v>
       </c>
       <c r="M97">
-        <v>92.39253772502298</v>
+        <v>93.36509075370743</v>
       </c>
       <c r="N97">
-        <v>-55.67553772502298</v>
+        <v>-56.64809075370744</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-55.67553772502298</v>
+        <v>-56.64809075370744</v>
       </c>
       <c r="Q97">
-        <v>-54.91153772502297</v>
+        <v>-55.88409075370743</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4812792761181178</v>
+        <v>0.5901490951476475</v>
       </c>
       <c r="T97">
-        <v>8.488301648692508</v>
+        <v>10.61037706086564</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3974022242930103</v>
+        <v>0.3932626177899581</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2499739638059059</v>
+        <v>0.2518739638059059</v>
       </c>
       <c r="C98">
-        <v>-187.0621570321716</v>
+        <v>-191.8990412776051</v>
       </c>
       <c r="D98">
-        <v>103.9881854347809</v>
+        <v>103.2757839233782</v>
       </c>
       <c r="E98">
-        <v>393.5020690638769</v>
+        <v>397.6265517979077</v>
       </c>
       <c r="F98">
-        <v>395.9503424669526</v>
+        <v>400.0748252009834</v>
       </c>
       <c r="G98">
         <v>104.9</v>
@@ -9329,28 +9329,28 @@
         <v>36.717</v>
       </c>
       <c r="M98">
-        <v>93.36509075370742</v>
+        <v>94.33764378239188</v>
       </c>
       <c r="N98">
-        <v>-56.64809075370742</v>
+        <v>-57.62064378239188</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-56.64809075370742</v>
+        <v>-57.62064378239188</v>
       </c>
       <c r="Q98">
-        <v>-55.88409075370742</v>
+        <v>-56.85664378239188</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.590149095147646</v>
+        <v>0.7715987935301947</v>
       </c>
       <c r="T98">
-        <v>10.61037706086561</v>
+        <v>14.14716941448748</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3932626177899582</v>
+        <v>0.389208363998309</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2518739638059059</v>
+        <v>0.2537739638059059</v>
       </c>
       <c r="C99">
-        <v>-191.8990412776051</v>
+        <v>-196.7262309085526</v>
       </c>
       <c r="D99">
-        <v>103.2757839233782</v>
+        <v>102.5730770264615</v>
       </c>
       <c r="E99">
-        <v>397.6265517979077</v>
+        <v>401.7510345319385</v>
       </c>
       <c r="F99">
-        <v>400.0748252009834</v>
+        <v>404.1993079350141</v>
       </c>
       <c r="G99">
         <v>104.9</v>
@@ -9411,28 +9411,28 @@
         <v>36.717</v>
       </c>
       <c r="M99">
-        <v>94.33764378239188</v>
+        <v>95.31019681107634</v>
       </c>
       <c r="N99">
-        <v>-57.62064378239188</v>
+        <v>-58.59319681107634</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-57.62064378239188</v>
+        <v>-58.59319681107634</v>
       </c>
       <c r="Q99">
-        <v>-56.85664378239188</v>
+        <v>-57.82919681107634</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7715987935301947</v>
+        <v>1.134498190295292</v>
       </c>
       <c r="T99">
-        <v>14.14716941448748</v>
+        <v>21.22075412173122</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.389208363998309</v>
+        <v>0.385236850079959</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2537739638059059</v>
+        <v>0.2556739638059058</v>
       </c>
       <c r="C100">
-        <v>-196.7262309085526</v>
+        <v>-201.5439224792939</v>
       </c>
       <c r="D100">
-        <v>102.5730770264615</v>
+        <v>101.8798681897509</v>
       </c>
       <c r="E100">
-        <v>401.7510345319385</v>
+        <v>405.8755172659692</v>
       </c>
       <c r="F100">
-        <v>404.1993079350141</v>
+        <v>408.3237906690449</v>
       </c>
       <c r="G100">
         <v>104.9</v>
@@ -9493,28 +9493,28 @@
         <v>36.717</v>
       </c>
       <c r="M100">
-        <v>95.31019681107634</v>
+        <v>96.28274983976078</v>
       </c>
       <c r="N100">
-        <v>-58.59319681107634</v>
+        <v>-59.56574983976078</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-58.59319681107634</v>
+        <v>-59.56574983976078</v>
       </c>
       <c r="Q100">
-        <v>-57.82919681107634</v>
+        <v>-58.80174983976078</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.134498190295292</v>
+        <v>2.223196380590584</v>
       </c>
       <c r="T100">
-        <v>21.22075412173122</v>
+        <v>42.44150824346244</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.385236850079959</v>
+        <v>0.38134556876602</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2556739638059058</v>
-      </c>
-      <c r="C101">
-        <v>-201.5439224792939</v>
-      </c>
-      <c r="D101">
-        <v>101.8798681897509</v>
-      </c>
-      <c r="E101">
-        <v>405.8755172659692</v>
-      </c>
-      <c r="F101">
-        <v>408.3237906690449</v>
-      </c>
-      <c r="G101">
-        <v>104.9</v>
-      </c>
-      <c r="H101">
-        <v>410</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37.481</v>
-      </c>
-      <c r="K101">
-        <v>0.764</v>
-      </c>
-      <c r="L101">
-        <v>36.717</v>
-      </c>
-      <c r="M101">
-        <v>96.28274983976078</v>
-      </c>
-      <c r="N101">
-        <v>-59.56574983976078</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-59.56574983976078</v>
-      </c>
-      <c r="Q101">
-        <v>-58.80174983976078</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.223196380590584</v>
-      </c>
-      <c r="T101">
-        <v>42.44150824346244</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.38134556876602</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
